--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_RCA_B03_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_RCA_B03_Normal_1.xlsx
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>18.59577612148967</v>
+        <v>18.5958571424894</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>18.32653818472934</v>
+        <v>18.32620723151755</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>17.39869466474527</v>
+        <v>17.3983048003378</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>16.20418723072947</v>
+        <v>16.20302300939407</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>15.92273468298473</v>
+        <v>15.9229719778835</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>15.72161634555431</v>
+        <v>15.72084198098498</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>15.5507438079188</v>
+        <v>15.55101988787667</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>14.88992375158841</v>
+        <v>14.89016779089395</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>14.71246574563552</v>
+        <v>14.71088301485738</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>14.30569448186231</v>
+        <v>14.30608443092145</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>14.1161048968173</v>
+        <v>14.11445294820949</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>14.1161048968173</v>
+        <v>14.11445294820949</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>13.69654197158049</v>
+        <v>13.69674140820063</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>13.67593720147719</v>
+        <v>13.67612557269601</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>13.75518931834387</v>
+        <v>13.75521870006</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>13.75518931834387</v>
+        <v>13.75555580580757</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>13.75561435417294</v>
+        <v>13.75566436755932</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>13.80966048283381</v>
+        <v>13.80951927004571</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>13.84215738492702</v>
+        <v>13.84208900190093</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>13.88152030731969</v>
+        <v>13.88136924118995</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>13.97927381896623</v>
+        <v>13.97919272526585</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>13.97966286717242</v>
+        <v>13.98027659518173</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>14.25882197659803</v>
+        <v>14.26125835165209</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>14.50952067138669</v>
+        <v>14.51204101624726</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>14.69579680606235</v>
+        <v>14.69817502425903</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>14.76209033990039</v>
+        <v>14.76185030831645</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>14.81511096602196</v>
+        <v>14.81501009309454</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>14.79356060599723</v>
+        <v>14.79368611294623</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>14.79356060599723</v>
+        <v>14.79368611294623</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>14.75836686993625</v>
+        <v>14.75842045723767</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>14.75130981487555</v>
+        <v>14.75135969545987</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>14.78919673645947</v>
+        <v>14.78882354574478</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>14.86348139582422</v>
+        <v>14.86295645256005</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>15.07594673414085</v>
+        <v>15.07551304456703</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>15.11430027839798</v>
+        <v>15.11449681792856</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>15.21247739041541</v>
+        <v>15.2128772616736</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>15.23268774912472</v>
+        <v>15.23312150372263</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>15.23268774912472</v>
+        <v>15.23312150372263</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>15.25436071244039</v>
+        <v>15.254133516272</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>15.28142901183043</v>
+        <v>15.28144353047945</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>15.47278171594387</v>
+        <v>15.48663624119257</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>15.47586546823703</v>
+        <v>15.49445685593772</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>15.47586546823703</v>
+        <v>15.49445685593772</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>15.59002034008771</v>
+        <v>15.60725081452069</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>15.59002034008771</v>
+        <v>15.60725081452069</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>15.66445665070604</v>
+        <v>15.6476327842228</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>15.66951878819829</v>
+        <v>15.65580164839136</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>15.77263732024918</v>
+        <v>15.75140669796794</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>15.77263732024918</v>
+        <v>15.75140669796794</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>15.77453240476826</v>
+        <v>15.73645483296908</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>15.77784259658588</v>
+        <v>15.77803283344071</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>15.84585891055596</v>
+        <v>15.83820595608971</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>15.84585891055596</v>
+        <v>15.83820595608971</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>16.08447504296169</v>
+        <v>16.0616378685357</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>16.08447504296169</v>
+        <v>16.0616378685357</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>16.36056433652246</v>
+        <v>16.36088206670063</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>16.37148370350915</v>
+        <v>16.37005654881354</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>16.34482841651914</v>
+        <v>16.3436156314035</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>16.2653976834007</v>
+        <v>16.26501766840735</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>16.24898257398155</v>
+        <v>16.24607503639474</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>16.20144569466017</v>
+        <v>16.24607503639474</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>16.1393539978375</v>
+        <v>16.19424984083999</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>15.96103263279966</v>
+        <v>15.95765904539337</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>15.96103263279966</v>
+        <v>15.95765904539337</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>15.84818640904148</v>
+        <v>15.84864908751183</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>15.78572574054218</v>
+        <v>15.7843096262815</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>15.78572574054218</v>
+        <v>15.7843096262815</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>15.74356579603598</v>
+        <v>15.73858644260433</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>15.74096221433212</v>
+        <v>15.73112189854901</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>15.74096221433212</v>
+        <v>15.73112189854901</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>15.66583729643611</v>
+        <v>15.65601885349941</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>15.5723268510037</v>
+        <v>15.56892071370931</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>15.5723268510037</v>
+        <v>15.56892071370931</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>15.45829858881812</v>
+        <v>15.45844330792743</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>15.48567353913612</v>
+        <v>15.48575214444639</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>15.48637721293284</v>
+        <v>15.48575214444639</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>15.50131463330612</v>
+        <v>15.50101837053016</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>15.4992725478057</v>
+        <v>15.49530138058276</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>15.38412686271078</v>
+        <v>15.37806196163589</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>15.30303052973483</v>
+        <v>15.29546624441339</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>15.12333548665893</v>
+        <v>15.20839369188793</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>15.12333548665893</v>
+        <v>15.12295722797956</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>14.93123165826102</v>
+        <v>14.92806150007394</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>14.88153602107888</v>
+        <v>14.87431930601249</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>14.67478106861882</v>
+        <v>14.67407824912346</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>14.52649765210695</v>
+        <v>14.65217302852508</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>14.51878306129579</v>
+        <v>14.50427649021133</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>14.37354135558389</v>
+        <v>14.35909241243977</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>14.24685234354893</v>
+        <v>14.24643935632847</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>14.2414595735651</v>
+        <v>14.231724131751</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>14.15429193600505</v>
+        <v>14.231724131751</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>14.15429193600505</v>
+        <v>14.15391152919285</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>13.84448162694595</v>
+        <v>13.84254841009699</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>13.84963526742995</v>
+        <v>13.84973860734367</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>13.85110562161235</v>
+        <v>13.85379692286522</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>13.87800091620979</v>
+        <v>13.87804146428957</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>13.62624297796148</v>
+        <v>13.62608019071382</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>13.55073419737553</v>
+        <v>13.54824482014322</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>13.26736758397264</v>
+        <v>13.26729517339624</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>13.16936893002901</v>
+        <v>13.16255095651221</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>13.07244254921576</v>
+        <v>13.07238808670398</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>13.00942747074897</v>
+        <v>13.00513144905946</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>12.91776612718095</v>
+        <v>12.96033786024594</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>12.9275215398158</v>
+        <v>12.92758743496764</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>12.96218725171638</v>
+        <v>12.9649053093511</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>12.9857488123543</v>
+        <v>12.98938397985515</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>13.02866128079873</v>
+        <v>13.01887008375784</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>13.02850885339891</v>
+        <v>13.02837781256831</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>13.00402198653148</v>
+        <v>13.00399646376883</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>13.00177319819151</v>
+        <v>12.99777651565076</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>12.83928864017555</v>
+        <v>12.83081986735597</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>12.70944477256218</v>
+        <v>12.71383377636713</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>12.49503518787352</v>
+        <v>12.49488711964402</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="K115" t="n">
-        <v>12.34808261586839</v>
+        <v>12.33215037197922</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>12.23464380168823</v>
+        <v>12.23484589986313</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="n">
-        <v>11.67678387947476</v>
+        <v>11.66069996340032</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>11.56246379376206</v>
+        <v>11.54972939425211</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>11.48242352698332</v>
+        <v>11.47490649554457</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>11.41805538019941</v>
+        <v>11.41581537788513</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="n">
-        <v>11.48903081177367</v>
+        <v>11.4982694787367</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>2</v>
       </c>
       <c r="K122" t="n">
-        <v>11.48903081177367</v>
+        <v>11.4982694787367</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>2</v>
       </c>
       <c r="K123" t="n">
-        <v>11.48903081177367</v>
+        <v>11.4982694787367</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>11.54636318163965</v>
+        <v>11.55749010887987</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>11.76181036195703</v>
+        <v>11.76596897696077</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>12.01438835609347</v>
+        <v>12.01262717872386</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>12.02133088238046</v>
+        <v>12.03204926583027</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>12.20109228741248</v>
+        <v>12.19993626993534</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>12.21077046290756</v>
+        <v>12.22776251370118</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>12.32249541189157</v>
+        <v>12.32193519376122</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>12.40949353695521</v>
+        <v>12.41754142527532</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>12.40949353695521</v>
+        <v>12.41754142527532</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>12.45263424891663</v>
+        <v>12.45741448570714</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>12.48192984726277</v>
+        <v>12.48211446144651</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>12.69235370693736</v>
+        <v>12.69301675853099</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>13.02732477002593</v>
+        <v>13.02817159258652</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>13.02732477002593</v>
+        <v>13.02817159258652</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>13.51095058914278</v>
+        <v>13.51857413985321</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>13.99624930190914</v>
+        <v>14.00295309632842</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>14.11986885589358</v>
+        <v>14.11961434555307</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>14.48827219446171</v>
+        <v>14.48853281588636</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>14.49484036461602</v>
+        <v>14.49852708614872</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>14.58340025748786</v>
+        <v>14.58559881928498</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>14.54630851243538</v>
+        <v>14.54609549163953</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>14.17222930208726</v>
+        <v>14.22541599656543</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>14.16598972456144</v>
+        <v>14.15450526909428</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>14.01785378966837</v>
+        <v>14.01764541438872</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>14.01242866373197</v>
+        <v>14.01182918868243</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>14.08755780446031</v>
+        <v>14.09644173505593</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>14.20862678874008</v>
+        <v>14.20883851989587</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>2</v>
       </c>
       <c r="K151" t="n">
-        <v>14.48536169859559</v>
+        <v>14.4878118294874</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>14.5195596487109</v>
+        <v>14.51960021407257</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>14.53543797405462</v>
+        <v>14.53433904663515</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>14.4430763974908</v>
+        <v>14.43680280909084</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>14.40857392530264</v>
+        <v>14.40283158195211</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>14.40857392530264</v>
+        <v>14.40283158195211</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>14.24877187089477</v>
+        <v>14.24859817117511</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>14.24877187089477</v>
+        <v>14.24859817117511</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>14.13787674211844</v>
+        <v>14.14671896325551</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>13.96162479076668</v>
+        <v>13.96159051282686</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>13.95343428764751</v>
+        <v>13.93852644721354</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>2</v>
       </c>
       <c r="K162" t="n">
-        <v>13.66790413095648</v>
+        <v>13.6585389909501</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>13.66790413095648</v>
+        <v>13.6585389909501</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>13.5889364215805</v>
+        <v>13.58435746951348</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>13.5893343189891</v>
+        <v>13.58931592285176</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>13.656026907465</v>
+        <v>13.6556511668035</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>13.72057430562602</v>
+        <v>13.72056152886857</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>13.75079159207247</v>
+        <v>13.75077895035413</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>13.75418751938509</v>
+        <v>13.76005262742066</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>13.69959246327574</v>
+        <v>13.697135801276</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>13.69959246327574</v>
+        <v>13.69128677835532</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>13.57544585214279</v>
+        <v>13.57559038092814</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>2</v>
       </c>
       <c r="K173" t="n">
-        <v>13.30843032798533</v>
+        <v>13.30855849470719</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>13.24988442274572</v>
+        <v>13.25001988348301</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>13.24310869267457</v>
+        <v>13.23955014900721</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>2</v>
       </c>
       <c r="K176" t="n">
-        <v>13.16970930725598</v>
+        <v>13.1538097732883</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>2</v>
       </c>
       <c r="K177" t="n">
-        <v>12.78988920952387</v>
+        <v>12.7901466520401</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>12.59455440181871</v>
+        <v>12.594858471376</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>2</v>
       </c>
       <c r="K179" t="n">
-        <v>12.43291865117834</v>
+        <v>12.42166630359216</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>12.33309478240678</v>
+        <v>12.3330667768033</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>12.33286978191248</v>
+        <v>12.33386383492323</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>12.33286978191248</v>
+        <v>12.33386383492323</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>2</v>
       </c>
       <c r="K183" t="n">
-        <v>12.33286978191248</v>
+        <v>12.33386383492323</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>2</v>
       </c>
       <c r="K184" t="n">
-        <v>12.44282654205479</v>
+        <v>12.44623753451256</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>2</v>
       </c>
       <c r="K185" t="n">
-        <v>13.00882973111909</v>
+        <v>13.03770405702662</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>2</v>
       </c>
       <c r="K186" t="n">
-        <v>13.13909859932027</v>
+        <v>13.1368166780724</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="n">
-        <v>13.54463715220424</v>
+        <v>13.54885618105343</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>2</v>
       </c>
       <c r="K188" t="n">
-        <v>13.53049158976291</v>
+        <v>13.53070403717064</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>2</v>
       </c>
       <c r="K189" t="n">
-        <v>13.52852280151508</v>
+        <v>13.52954345434181</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>2</v>
       </c>
       <c r="K190" t="n">
-        <v>13.45869310177932</v>
+        <v>13.45920413813685</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>2</v>
       </c>
       <c r="K191" t="n">
-        <v>13.44879095727898</v>
+        <v>13.44400445575972</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>2</v>
       </c>
       <c r="K192" t="n">
-        <v>13.37988826484104</v>
+        <v>13.3761723954404</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>13.37988826484104</v>
+        <v>13.36651716300588</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>2</v>
       </c>
       <c r="K194" t="n">
-        <v>13.2236515063163</v>
+        <v>13.22432140839687</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>2</v>
       </c>
       <c r="K195" t="n">
-        <v>12.99027127132794</v>
+        <v>12.99102962350433</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>2</v>
       </c>
       <c r="K196" t="n">
-        <v>12.84157228517397</v>
+        <v>12.81307579997706</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>2</v>
       </c>
       <c r="K197" t="n">
-        <v>12.59244882332062</v>
+        <v>12.59323189767593</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>2</v>
       </c>
       <c r="K198" t="n">
-        <v>12.47175049640355</v>
+        <v>12.45164942446125</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>2</v>
       </c>
       <c r="K199" t="n">
-        <v>12.13996314156772</v>
+        <v>12.14009768864388</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>2</v>
       </c>
       <c r="K200" t="n">
-        <v>12.14370233812433</v>
+        <v>12.14870182130599</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>2</v>
       </c>
       <c r="K201" t="n">
-        <v>12.3762481477129</v>
+        <v>12.39283835234811</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>2</v>
       </c>
       <c r="K202" t="n">
-        <v>12.59773638129766</v>
+        <v>12.57295559523497</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>2</v>
       </c>
       <c r="K203" t="n">
-        <v>12.60171878130905</v>
+        <v>12.6025988850949</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>2</v>
       </c>
       <c r="K204" t="n">
-        <v>12.62645715330524</v>
+        <v>12.61837680870393</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>2</v>
       </c>
       <c r="K205" t="n">
-        <v>12.67595745355509</v>
+        <v>12.67735394878311</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>2</v>
       </c>
       <c r="K206" t="n">
-        <v>12.67595745355509</v>
+        <v>12.64042579689023</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>2</v>
       </c>
       <c r="K207" t="n">
-        <v>12.67595745355509</v>
+        <v>12.64042579689023</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>2</v>
       </c>
       <c r="K208" t="n">
-        <v>12.7018922598196</v>
+        <v>12.77607937342256</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>2</v>
       </c>
       <c r="K209" t="n">
-        <v>12.81043431165489</v>
+        <v>12.81073314733985</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>2</v>
       </c>
       <c r="K210" t="n">
-        <v>12.93928852695545</v>
+        <v>12.94321809827673</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>2</v>
       </c>
       <c r="K211" t="n">
-        <v>13.05604763158988</v>
+        <v>13.05579825726659</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>2</v>
       </c>
       <c r="K212" t="n">
-        <v>13.05604763158988</v>
+        <v>13.05579825726659</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>2</v>
       </c>
       <c r="K213" t="n">
-        <v>13.1074435818508</v>
+        <v>13.10985376737644</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>2</v>
       </c>
       <c r="K214" t="n">
-        <v>13.13682942462308</v>
+        <v>13.12703505446839</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>2</v>
       </c>
       <c r="K215" t="n">
-        <v>13.21621934149741</v>
+        <v>13.21642982401907</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>2</v>
       </c>
       <c r="K216" t="n">
-        <v>13.2193250182273</v>
+        <v>13.22245072917357</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>2</v>
       </c>
       <c r="K217" t="n">
-        <v>13.2193250182273</v>
+        <v>13.22245072917357</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>2</v>
       </c>
       <c r="K218" t="n">
-        <v>13.56011711963198</v>
+        <v>13.5621230211431</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>2</v>
       </c>
       <c r="K219" t="n">
-        <v>14.20564246881879</v>
+        <v>14.21781243721427</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>2</v>
       </c>
       <c r="K220" t="n">
-        <v>14.4682140102236</v>
+        <v>14.48362740730565</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>2</v>
       </c>
       <c r="K221" t="n">
-        <v>14.7661344551793</v>
+        <v>14.75391083746124</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="n">
-        <v>14.80342615480466</v>
+        <v>14.82422856261458</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="n">
-        <v>15.11894218385983</v>
+        <v>15.13568278504107</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>2</v>
       </c>
       <c r="K224" t="n">
-        <v>15.33049281757301</v>
+        <v>15.32781947637475</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>2</v>
       </c>
       <c r="K225" t="n">
-        <v>15.35416205571565</v>
+        <v>15.36240969261463</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>2</v>
       </c>
       <c r="K226" t="n">
-        <v>15.42306596395216</v>
+        <v>15.42365131613941</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>2</v>
       </c>
       <c r="K227" t="n">
-        <v>15.42306596395216</v>
+        <v>15.42365131613941</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>2</v>
       </c>
       <c r="K228" t="n">
-        <v>15.7556455577446</v>
+        <v>15.74989013717516</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>2</v>
       </c>
       <c r="K229" t="n">
-        <v>15.81216670730607</v>
+        <v>15.83651139689793</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>2</v>
       </c>
       <c r="K230" t="n">
-        <v>16.197614417865</v>
+        <v>16.1907074656956</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>2</v>
       </c>
       <c r="K231" t="n">
-        <v>17.06909492018154</v>
+        <v>17.06784684351383</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>2</v>
       </c>
       <c r="K232" t="n">
-        <v>17.16662005744153</v>
+        <v>17.16606445218712</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>2</v>
       </c>
       <c r="K233" t="n">
-        <v>17.1117281488238</v>
+        <v>17.11502833633417</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>2</v>
       </c>
       <c r="K234" t="n">
-        <v>10.61911050223006</v>
+        <v>10.61377793339147</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>2</v>
       </c>
       <c r="K235" t="n">
-        <v>10.61911050223006</v>
+        <v>10.61377793339147</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>2</v>
       </c>
       <c r="K236" t="n">
-        <v>10.54956869659312</v>
+        <v>10.54537378241061</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>2</v>
       </c>
       <c r="K237" t="n">
-        <v>10.39245568984219</v>
+        <v>10.39415596162064</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>2</v>
       </c>
       <c r="K238" t="n">
-        <v>10.2265489363392</v>
+        <v>10.22764271249716</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>2</v>
       </c>
       <c r="K239" t="n">
-        <v>10.2152109504431</v>
+        <v>10.21048345049517</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>2</v>
       </c>
       <c r="K240" t="n">
-        <v>10.05769889923186</v>
+        <v>10.05814027948479</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>2</v>
       </c>
       <c r="K241" t="n">
-        <v>10.03421169352104</v>
+        <v>10.0346401608808</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>2</v>
       </c>
       <c r="K242" t="n">
-        <v>9.967741768854573</v>
+        <v>9.966295663677505</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>2</v>
       </c>
       <c r="K243" t="n">
-        <v>9.959259860984305</v>
+        <v>9.958788632187566</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>2</v>
       </c>
       <c r="K244" t="n">
-        <v>9.977783248295985</v>
+        <v>9.977987516676835</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>2</v>
       </c>
       <c r="K245" t="n">
-        <v>10.01104760399325</v>
+        <v>10.01319952971685</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>2</v>
       </c>
       <c r="K246" t="n">
-        <v>10.14298070133031</v>
+        <v>10.14628358492826</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>2</v>
       </c>
       <c r="K247" t="n">
-        <v>10.18644318202784</v>
+        <v>10.18378705441236</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>2</v>
       </c>
       <c r="K248" t="n">
-        <v>10.18644318202784</v>
+        <v>10.18378705441236</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>2</v>
       </c>
       <c r="K249" t="n">
-        <v>10.36184713536416</v>
+        <v>10.35749540972766</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>2</v>
       </c>
       <c r="K250" t="n">
-        <v>10.36184713536416</v>
+        <v>10.35749540972766</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>2</v>
       </c>
       <c r="K251" t="n">
-        <v>10.40990095827578</v>
+        <v>10.40971923425729</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>2</v>
       </c>
       <c r="K252" t="n">
-        <v>10.48162678083738</v>
+        <v>10.48502381394126</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>2</v>
       </c>
       <c r="K253" t="n">
-        <v>10.67209273952509</v>
+        <v>10.67136372932887</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>2</v>
       </c>
       <c r="K254" t="n">
-        <v>10.6803584923927</v>
+        <v>10.68402992217249</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>2</v>
       </c>
       <c r="K255" t="n">
-        <v>10.73492205844875</v>
+        <v>10.73960284463619</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>2</v>
       </c>
       <c r="K256" t="n">
-        <v>10.80254216839109</v>
+        <v>10.80762898567785</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>2</v>
       </c>
       <c r="K257" t="n">
-        <v>10.94532996592256</v>
+        <v>10.94944799004153</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>2</v>
       </c>
       <c r="K258" t="n">
-        <v>10.94628942506596</v>
+        <v>10.94636415497368</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>2</v>
       </c>
       <c r="K259" t="n">
-        <v>10.92006187941307</v>
+        <v>10.92020790152956</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>2</v>
       </c>
       <c r="K260" t="n">
-        <v>10.91655562209516</v>
+        <v>10.91486666924119</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>2</v>
       </c>
       <c r="K261" t="n">
-        <v>10.9030034556844</v>
+        <v>10.90267107195267</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>2</v>
       </c>
       <c r="K262" t="n">
-        <v>10.90131390796726</v>
+        <v>10.90045952738595</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>2</v>
       </c>
       <c r="K263" t="n">
-        <v>10.90131390796726</v>
+        <v>10.90045952738595</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>2</v>
       </c>
       <c r="K264" t="n">
-        <v>11.00513265786821</v>
+        <v>11.00877464766869</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>2</v>
       </c>
       <c r="K265" t="n">
-        <v>11.26405288203294</v>
+        <v>11.26041926312474</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>2</v>
       </c>
       <c r="K266" t="n">
-        <v>11.68775398053865</v>
+        <v>11.69386578219394</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>2</v>
       </c>
       <c r="K267" t="n">
-        <v>11.74906546637305</v>
+        <v>11.75237327330915</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>2</v>
       </c>
       <c r="K268" t="n">
-        <v>11.74906546637305</v>
+        <v>11.75237327330915</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>2</v>
       </c>
       <c r="K269" t="n">
-        <v>11.90332308504306</v>
+        <v>11.90342691288019</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>2</v>
       </c>
       <c r="K270" t="n">
-        <v>12.0420021133997</v>
+        <v>12.03911505002709</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>2</v>
       </c>
       <c r="K271" t="n">
-        <v>12.0420021133997</v>
+        <v>12.03911505002709</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>2</v>
       </c>
       <c r="K272" t="n">
-        <v>12.14577831819476</v>
+        <v>12.14559473104569</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>2</v>
       </c>
       <c r="K273" t="n">
-        <v>12.15568184948754</v>
+        <v>12.1535207975502</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>2</v>
       </c>
       <c r="K274" t="n">
-        <v>12.13345641979544</v>
+        <v>12.13354727904132</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>2</v>
       </c>
       <c r="K275" t="n">
-        <v>12.08853258813774</v>
+        <v>12.08500590997779</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>2</v>
       </c>
       <c r="K276" t="n">
-        <v>11.99233399122049</v>
+        <v>11.99256177293214</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>2</v>
       </c>
       <c r="K277" t="n">
-        <v>11.81949609990912</v>
+        <v>11.88590103555119</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>2</v>
       </c>
       <c r="K278" t="n">
-        <v>11.81949609990912</v>
+        <v>11.82166550968323</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>2</v>
       </c>
       <c r="K279" t="n">
-        <v>11.72678628653808</v>
+        <v>11.72977684074582</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K280" t="n">
-        <v>11.72678628653808</v>
+        <v>11.72977684074582</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>2</v>
       </c>
       <c r="K281" t="n">
-        <v>11.63022948752821</v>
+        <v>11.6303233410911</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>2</v>
       </c>
       <c r="K282" t="n">
-        <v>11.63022948752821</v>
+        <v>11.6303233410911</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>2</v>
       </c>
       <c r="K283" t="n">
-        <v>11.41827384702243</v>
+        <v>11.40836386312312</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>2</v>
       </c>
       <c r="K284" t="n">
-        <v>11.24699157557455</v>
+        <v>11.24608596661873</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>2</v>
       </c>
       <c r="K285" t="n">
-        <v>11.24200494202111</v>
+        <v>11.24015463105883</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>2</v>
       </c>
       <c r="K286" t="n">
-        <v>11.23722958745733</v>
+        <v>11.23632590927421</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>2</v>
       </c>
       <c r="K287" t="n">
-        <v>11.23722958745733</v>
+        <v>11.23632590927421</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>11.23717747288252</v>
+        <v>11.23591390864401</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>2</v>
       </c>
       <c r="K289" t="n">
-        <v>11.24408702631454</v>
+        <v>11.24144554213679</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>2</v>
       </c>
       <c r="K290" t="n">
-        <v>11.269655733759</v>
+        <v>11.24567912461699</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>2</v>
       </c>
       <c r="K291" t="n">
-        <v>11.27743995595575</v>
+        <v>11.27989355584175</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>2</v>
       </c>
       <c r="K292" t="n">
-        <v>11.36475961214373</v>
+        <v>11.3642894428055</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>2</v>
       </c>
       <c r="K293" t="n">
-        <v>11.45347848176825</v>
+        <v>11.45305438543651</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>2</v>
       </c>
       <c r="K294" t="n">
-        <v>11.5002703110434</v>
+        <v>11.4998860203704</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>2</v>
       </c>
       <c r="K295" t="n">
-        <v>11.50289523916865</v>
+        <v>11.50170273597373</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>2</v>
       </c>
       <c r="K296" t="n">
-        <v>11.64392494349398</v>
+        <v>11.65066919868475</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>2</v>
       </c>
       <c r="K297" t="n">
-        <v>11.64392494349398</v>
+        <v>11.65066919868475</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>2</v>
       </c>
       <c r="K298" t="n">
-        <v>12.05399660846981</v>
+        <v>12.05365340163475</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>2</v>
       </c>
       <c r="K299" t="n">
-        <v>12.24909592069416</v>
+        <v>12.24898459833241</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>2</v>
       </c>
       <c r="K300" t="n">
-        <v>12.30368029765579</v>
+        <v>12.29627786312138</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>2</v>
       </c>
       <c r="K301" t="n">
-        <v>12.30368029765579</v>
+        <v>12.29627786312138</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>2</v>
       </c>
       <c r="K302" t="n">
-        <v>12.37801436891967</v>
+        <v>12.37786687442085</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>2</v>
       </c>
       <c r="K303" t="n">
-        <v>12.26175677687068</v>
+        <v>12.26110024580426</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>2</v>
       </c>
       <c r="K304" t="n">
-        <v>12.20987939473963</v>
+        <v>12.21036683952809</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>2</v>
       </c>
       <c r="K305" t="n">
-        <v>12.19809213904041</v>
+        <v>12.19710995149599</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>2</v>
       </c>
       <c r="K306" t="n">
-        <v>12.17563696457241</v>
+        <v>12.17461009295258</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>2</v>
       </c>
       <c r="K307" t="n">
-        <v>12.15869311624666</v>
+        <v>12.15700496953431</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>2</v>
       </c>
       <c r="K308" t="n">
-        <v>12.03888124284176</v>
+        <v>12.0337526186164</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>2</v>
       </c>
       <c r="K309" t="n">
-        <v>11.94402285359583</v>
+        <v>11.94415552794555</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>2</v>
       </c>
       <c r="K310" t="n">
-        <v>11.88569263406168</v>
+        <v>11.88580735286103</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>2</v>
       </c>
       <c r="K311" t="n">
-        <v>11.67339021670546</v>
+        <v>11.66508816235581</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>2</v>
       </c>
       <c r="K312" t="n">
-        <v>11.60835187874535</v>
+        <v>11.60858562866873</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>2</v>
       </c>
       <c r="K313" t="n">
-        <v>11.59179901159414</v>
+        <v>11.58295503969272</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>2</v>
       </c>
       <c r="K314" t="n">
-        <v>11.50342232457231</v>
+        <v>11.49495191954461</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>2</v>
       </c>
       <c r="K315" t="n">
-        <v>11.43027320451526</v>
+        <v>11.42367176615113</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>2</v>
       </c>
       <c r="K316" t="n">
-        <v>11.25846702058127</v>
+        <v>11.25552943272468</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>2</v>
       </c>
       <c r="K317" t="n">
-        <v>11.21783190205098</v>
+        <v>11.21830962088214</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>2</v>
       </c>
       <c r="K318" t="n">
-        <v>11.20615079005939</v>
+        <v>11.2061481912685</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>2</v>
       </c>
       <c r="K319" t="n">
-        <v>11.2026724842647</v>
+        <v>11.20265768987954</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>2</v>
       </c>
       <c r="K320" t="n">
-        <v>11.21167617905264</v>
+        <v>11.20970734106739</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>2</v>
       </c>
       <c r="K321" t="n">
-        <v>11.22626689551572</v>
+        <v>11.22610270869758</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>2</v>
       </c>
       <c r="K322" t="n">
-        <v>11.34123535822267</v>
+        <v>11.34055749923166</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>2</v>
       </c>
       <c r="K323" t="n">
-        <v>11.39712629634621</v>
+        <v>11.40311655366015</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>2</v>
       </c>
       <c r="K324" t="n">
-        <v>11.49579778548074</v>
+        <v>11.45938483020061</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>2</v>
       </c>
       <c r="K325" t="n">
-        <v>11.55398427338575</v>
+        <v>11.5695700098634</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="K326" t="n">
-        <v>11.83387072376867</v>
+        <v>11.85751394573535</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>2</v>
       </c>
       <c r="K327" t="n">
-        <v>11.92170865648094</v>
+        <v>11.91495074484171</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>2</v>
       </c>
       <c r="K328" t="n">
-        <v>11.92170865648094</v>
+        <v>11.91495074484171</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>2</v>
       </c>
       <c r="K329" t="n">
-        <v>12.17389355374015</v>
+        <v>12.13094515731134</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>2</v>
       </c>
       <c r="K330" t="n">
-        <v>12.0644342881679</v>
+        <v>12.04949934003083</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>2</v>
       </c>
       <c r="K331" t="n">
-        <v>11.92732515489163</v>
+        <v>11.92420880527066</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>2</v>
       </c>
       <c r="K332" t="n">
-        <v>11.92732515489163</v>
+        <v>11.92420880527066</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>2</v>
       </c>
       <c r="K333" t="n">
-        <v>11.59752871850242</v>
+        <v>11.58211452330169</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>2</v>
       </c>
       <c r="K334" t="n">
-        <v>11.38606094714189</v>
+        <v>11.38669301342711</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>2</v>
       </c>
       <c r="K335" t="n">
-        <v>11.1133268734165</v>
+        <v>11.09825445891859</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>2</v>
       </c>
       <c r="K336" t="n">
-        <v>11.00375576951976</v>
+        <v>10.99072455620695</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>2</v>
       </c>
       <c r="K337" t="n">
-        <v>10.91261522682275</v>
+        <v>10.90264832781277</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>2</v>
       </c>
       <c r="K338" t="n">
-        <v>10.74998710043919</v>
+        <v>10.74963121744483</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>2</v>
       </c>
       <c r="K339" t="n">
-        <v>10.72828747682155</v>
+        <v>10.73170944341776</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>2</v>
       </c>
       <c r="K340" t="n">
-        <v>10.71245890108268</v>
+        <v>10.71380131569459</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>2</v>
       </c>
       <c r="K341" t="n">
-        <v>10.66615379908576</v>
+        <v>10.65886029040991</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>2</v>
       </c>
       <c r="K342" t="n">
-        <v>10.59523314150151</v>
+        <v>10.58430469680095</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>2</v>
       </c>
       <c r="K343" t="n">
-        <v>10.33818247585249</v>
+        <v>10.33699819630408</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>2</v>
       </c>
       <c r="K344" t="n">
-        <v>10.23566740368244</v>
+        <v>10.22700231635053</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>2</v>
       </c>
       <c r="K345" t="n">
-        <v>10.246065646498</v>
+        <v>10.25409139807304</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>2</v>
       </c>
       <c r="K346" t="n">
-        <v>10.47342729765415</v>
+        <v>10.44169100312682</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>2</v>
       </c>
       <c r="K347" t="n">
-        <v>10.5810120033017</v>
+        <v>10.58154133565366</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>2</v>
       </c>
       <c r="K348" t="n">
-        <v>10.6285285101308</v>
+        <v>10.62902414837056</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>2</v>
       </c>
       <c r="K349" t="n">
-        <v>10.71115562468179</v>
+        <v>10.71169180146465</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>2</v>
       </c>
       <c r="K350" t="n">
-        <v>10.72194314896624</v>
+        <v>10.72820510119372</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>2</v>
       </c>
       <c r="K351" t="n">
-        <v>10.75018103185945</v>
+        <v>10.75000773162565</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>2</v>
       </c>
       <c r="K352" t="n">
-        <v>10.73062926186099</v>
+        <v>10.73049166684081</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>2</v>
       </c>
       <c r="K353" t="n">
-        <v>10.68614682812558</v>
+        <v>10.69472073674776</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>2</v>
       </c>
       <c r="K354" t="n">
-        <v>10.6846042231272</v>
+        <v>10.68481883651214</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>2</v>
       </c>
       <c r="K355" t="n">
-        <v>10.52285729231184</v>
+        <v>10.52351671766851</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>2</v>
       </c>
       <c r="K356" t="n">
-        <v>10.47187369775552</v>
+        <v>10.50600387239207</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>2</v>
       </c>
       <c r="K357" t="n">
-        <v>10.43858036452489</v>
+        <v>10.43833632130694</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>2</v>
       </c>
       <c r="K358" t="n">
-        <v>10.49624137226914</v>
+        <v>10.49681870862702</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>2</v>
       </c>
       <c r="K359" t="n">
-        <v>10.56678026663119</v>
+        <v>10.56735065006838</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>2</v>
       </c>
       <c r="K360" t="n">
-        <v>10.95610601459666</v>
+        <v>10.96208051305802</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>2</v>
       </c>
       <c r="K361" t="n">
-        <v>11.01366549204793</v>
+        <v>11.0105188873164</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>2</v>
       </c>
       <c r="K362" t="n">
-        <v>11.02506193209913</v>
+        <v>11.03310114689288</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>2</v>
       </c>
       <c r="K363" t="n">
-        <v>11.02506193209913</v>
+        <v>11.03310114689288</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>2</v>
       </c>
       <c r="K364" t="n">
-        <v>11.2542693675967</v>
+        <v>11.25827718493396</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>2</v>
       </c>
       <c r="K365" t="n">
-        <v>11.34701241165128</v>
+        <v>11.34856877300246</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>2</v>
       </c>
       <c r="K366" t="n">
-        <v>11.34701241165128</v>
+        <v>11.34856877300246</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>2</v>
       </c>
       <c r="K367" t="n">
-        <v>11.48380883964817</v>
+        <v>11.48409905029244</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>2</v>
       </c>
       <c r="K368" t="n">
-        <v>11.52323152430861</v>
+        <v>11.52342195633293</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>2</v>
       </c>
       <c r="K369" t="n">
-        <v>11.58966507413004</v>
+        <v>11.58969811462833</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>2</v>
       </c>
       <c r="K370" t="n">
-        <v>11.58966507413004</v>
+        <v>11.58969811462833</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>2</v>
       </c>
       <c r="K371" t="n">
-        <v>11.60940821469449</v>
+        <v>11.61053969247575</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>2</v>
       </c>
       <c r="K372" t="n">
-        <v>11.56437463297245</v>
+        <v>11.55765044352143</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>2</v>
       </c>
       <c r="K373" t="n">
-        <v>11.56437463297245</v>
+        <v>11.55765044352143</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>2</v>
       </c>
       <c r="K374" t="n">
-        <v>11.51365037275185</v>
+        <v>11.50692855754407</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>2</v>
       </c>
       <c r="K375" t="n">
-        <v>11.46611134977171</v>
+        <v>11.45959889613622</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>2</v>
       </c>
       <c r="K376" t="n">
-        <v>11.42101232460941</v>
+        <v>11.41486390617419</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>2</v>
       </c>
       <c r="K377" t="n">
-        <v>11.37772543432911</v>
+        <v>11.37183416415546</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>2</v>
       </c>
       <c r="K378" t="n">
-        <v>11.34958529219559</v>
+        <v>11.34847380725387</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>2</v>
       </c>
       <c r="K379" t="n">
-        <v>11.30333079242962</v>
+        <v>11.2969639370707</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>2</v>
       </c>
       <c r="K380" t="n">
-        <v>11.27399383888022</v>
+        <v>11.27141506467429</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>2</v>
       </c>
       <c r="K381" t="n">
-        <v>11.27399383888022</v>
+        <v>11.27141506467429</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>2</v>
       </c>
       <c r="K382" t="n">
-        <v>11.23161542005935</v>
+        <v>11.23329842807134</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>2</v>
       </c>
       <c r="K383" t="n">
-        <v>11.23161542005935</v>
+        <v>11.23329842807134</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>2</v>
       </c>
       <c r="K384" t="n">
-        <v>11.19482758736256</v>
+        <v>11.19223177321082</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>2</v>
       </c>
       <c r="K385" t="n">
-        <v>11.18079536492961</v>
+        <v>11.18036106776119</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>2</v>
       </c>
       <c r="K386" t="n">
-        <v>11.03835805646356</v>
+        <v>11.0379241368384</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>2</v>
       </c>
       <c r="K387" t="n">
-        <v>10.84285961863374</v>
+        <v>10.83937988052107</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>2</v>
       </c>
       <c r="K388" t="n">
-        <v>10.78193660456983</v>
+        <v>10.78154512863441</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>2</v>
       </c>
       <c r="K389" t="n">
-        <v>10.6388792735933</v>
+        <v>10.66484643829772</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>2</v>
       </c>
       <c r="K390" t="n">
-        <v>10.62961216909575</v>
+        <v>10.62708821394779</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>2</v>
       </c>
       <c r="K391" t="n">
-        <v>10.6479900009266</v>
+        <v>10.65132712266964</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>2</v>
       </c>
       <c r="K392" t="n">
-        <v>10.67385118728334</v>
+        <v>10.6777230608249</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>2</v>
       </c>
       <c r="K393" t="n">
-        <v>10.7968105163995</v>
+        <v>10.79696802094925</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>2</v>
       </c>
       <c r="K394" t="n">
-        <v>10.79710815444206</v>
+        <v>10.79702283151183</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>2</v>
       </c>
       <c r="K395" t="n">
-        <v>10.74403853252198</v>
+        <v>10.738251605265</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>2</v>
       </c>
       <c r="K396" t="n">
-        <v>10.69581270199281</v>
+        <v>10.68810379733626</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>2</v>
       </c>
       <c r="K397" t="n">
-        <v>10.65308895052651</v>
+        <v>10.65281273191179</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>2</v>
       </c>
       <c r="K398" t="n">
-        <v>10.57478811099957</v>
+        <v>10.57430864587566</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>2</v>
       </c>
       <c r="K399" t="n">
-        <v>10.39390959503273</v>
+        <v>10.39359763213632</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>2</v>
       </c>
       <c r="K400" t="n">
-        <v>10.3129398920503</v>
+        <v>10.31257834726612</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>2</v>
       </c>
       <c r="K401" t="n">
-        <v>10.23414491395603</v>
+        <v>10.28139409062015</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>2</v>
       </c>
       <c r="K402" t="n">
-        <v>10.06038416143481</v>
+        <v>10.04895655889977</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>2</v>
       </c>
       <c r="K403" t="n">
-        <v>10.06038416143481</v>
+        <v>10.04895655889977</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>2</v>
       </c>
       <c r="K404" t="n">
-        <v>9.977468383393177</v>
+        <v>9.994853259071899</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>2</v>
       </c>
       <c r="K405" t="n">
-        <v>9.907400334943294</v>
+        <v>9.909449846983383</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>2</v>
       </c>
       <c r="K406" t="n">
-        <v>9.810198921768906</v>
+        <v>9.80132476610676</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>2</v>
       </c>
       <c r="K407" t="n">
-        <v>9.695529746644</v>
+        <v>9.699825482893882</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>2</v>
       </c>
       <c r="K408" t="n">
-        <v>9.620126400637604</v>
+        <v>9.618335663193012</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>2</v>
       </c>
       <c r="K409" t="n">
-        <v>9.620126400637604</v>
+        <v>9.618335663193012</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>2</v>
       </c>
       <c r="K410" t="n">
-        <v>9.640467433170874</v>
+        <v>9.638622672400784</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>2</v>
       </c>
       <c r="K411" t="n">
-        <v>9.662502714379828</v>
+        <v>9.663944318623356</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>2</v>
       </c>
       <c r="K412" t="n">
-        <v>9.725447153439758</v>
+        <v>9.724605391475256</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>2</v>
       </c>
       <c r="K413" t="n">
-        <v>9.740926468144629</v>
+        <v>9.740833771986221</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>2</v>
       </c>
       <c r="K414" t="n">
-        <v>9.743440472171818</v>
+        <v>9.744215253740238</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>2</v>
       </c>
       <c r="K415" t="n">
-        <v>9.703289058860895</v>
+        <v>9.697645217622982</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>2</v>
       </c>
       <c r="K416" t="n">
-        <v>9.671920117602522</v>
+        <v>9.671749440824083</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>2</v>
       </c>
       <c r="K417" t="n">
-        <v>9.585049280241341</v>
+        <v>9.584911305318773</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>2</v>
       </c>
       <c r="K418" t="n">
-        <v>9.582084895948078</v>
+        <v>9.582886539201843</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>2</v>
       </c>
       <c r="K419" t="n">
-        <v>9.543757637883417</v>
+        <v>9.54031058006775</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>2</v>
       </c>
       <c r="K420" t="n">
-        <v>9.496572077923762</v>
+        <v>9.496656097909311</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>2</v>
       </c>
       <c r="K421" t="n">
-        <v>9.571162336849559</v>
+        <v>9.579117289938509</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>2</v>
       </c>
       <c r="K422" t="n">
-        <v>9.677463988893495</v>
+        <v>9.677629436208672</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>2</v>
       </c>
       <c r="K423" t="n">
-        <v>9.695695507769447</v>
+        <v>9.681130843897925</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>2</v>
       </c>
       <c r="K424" t="n">
-        <v>10.01120179158256</v>
+        <v>10.02270166051669</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>2</v>
       </c>
       <c r="K425" t="n">
-        <v>10.23019737869262</v>
+        <v>10.24264666835121</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>2</v>
       </c>
       <c r="K426" t="n">
-        <v>10.23019737869262</v>
+        <v>10.24264666835121</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>2</v>
       </c>
       <c r="K427" t="n">
-        <v>10.38393745448631</v>
+        <v>10.38197901795579</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>2</v>
       </c>
       <c r="K428" t="n">
-        <v>10.52584988094988</v>
+        <v>10.52416338395925</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>2</v>
       </c>
       <c r="K429" t="n">
-        <v>10.60243413639511</v>
+        <v>10.61084542767775</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>2</v>
       </c>
       <c r="K430" t="n">
-        <v>10.732383557057</v>
+        <v>10.7370274892658</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>2</v>
       </c>
       <c r="K431" t="n">
-        <v>10.75422227056978</v>
+        <v>10.75423913002098</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>2</v>
       </c>
       <c r="K432" t="n">
-        <v>10.78197531098849</v>
+        <v>10.77808735657225</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>2</v>
       </c>
       <c r="K433" t="n">
-        <v>10.78848522396359</v>
+        <v>10.78848119241354</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>2</v>
       </c>
       <c r="K434" t="n">
-        <v>10.75335280170176</v>
+        <v>10.75334344596491</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>2</v>
       </c>
       <c r="K435" t="n">
-        <v>10.68789550863576</v>
+        <v>10.6878215991045</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>2</v>
       </c>
       <c r="K436" t="n">
-        <v>10.67515280115071</v>
+        <v>10.66823872474756</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>2</v>
       </c>
       <c r="K437" t="n">
-        <v>10.57593069717764</v>
+        <v>10.56927574667487</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>2</v>
       </c>
       <c r="K438" t="n">
-        <v>10.5000729135364</v>
+        <v>10.50935207297594</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>2</v>
       </c>
       <c r="K439" t="n">
-        <v>10.5000729135364</v>
+        <v>10.4938293375324</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>2</v>
       </c>
       <c r="K440" t="n">
-        <v>10.38523578394051</v>
+        <v>10.38089804589707</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>2</v>
       </c>
       <c r="K441" t="n">
-        <v>10.38523578394051</v>
+        <v>10.38089804589707</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>2</v>
       </c>
       <c r="K442" t="n">
-        <v>10.34004892860301</v>
+        <v>10.340048752131</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>2</v>
       </c>
       <c r="K443" t="n">
-        <v>10.32954874938226</v>
+        <v>10.32626936952353</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>2</v>
       </c>
       <c r="K444" t="n">
-        <v>10.34427533699865</v>
+        <v>10.34425477330191</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>2</v>
       </c>
       <c r="K445" t="n">
-        <v>10.49292752023152</v>
+        <v>10.47161372917363</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>2</v>
       </c>
       <c r="K446" t="n">
-        <v>10.49292752023152</v>
+        <v>10.49286453812276</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>2</v>
       </c>
       <c r="K447" t="n">
-        <v>10.60742981268204</v>
+        <v>10.6068352934358</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>2</v>
       </c>
       <c r="K448" t="n">
-        <v>10.67604597807587</v>
+        <v>10.67480166427617</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>2</v>
       </c>
       <c r="K449" t="n">
-        <v>10.69621888372733</v>
+        <v>10.69047316238096</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>2</v>
       </c>
       <c r="K450" t="n">
-        <v>10.69621888372733</v>
+        <v>10.69047316238096</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>2</v>
       </c>
       <c r="K451" t="n">
-        <v>10.76229524076231</v>
+        <v>10.75777083526336</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>2</v>
       </c>
       <c r="K452" t="n">
-        <v>10.76229524076231</v>
+        <v>10.76715947797017</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>2</v>
       </c>
       <c r="K453" t="n">
-        <v>10.81670345038093</v>
+        <v>10.82101862428146</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>2</v>
       </c>
       <c r="K454" t="n">
-        <v>10.84462043904434</v>
+        <v>10.84878901186218</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>2</v>
       </c>
       <c r="K455" t="n">
-        <v>10.87771153473942</v>
+        <v>10.87777341249348</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>2</v>
       </c>
       <c r="K456" t="n">
-        <v>10.86973799323843</v>
+        <v>10.8762273790637</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>2</v>
       </c>
       <c r="K457" t="n">
-        <v>10.86973799323843</v>
+        <v>10.86544141875749</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>2</v>
       </c>
       <c r="K458" t="n">
-        <v>10.80590214121558</v>
+        <v>10.80600692064549</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>2</v>
       </c>
       <c r="K459" t="n">
-        <v>10.68259747929901</v>
+        <v>10.67433788526507</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>2</v>
       </c>
       <c r="K460" t="n">
-        <v>10.62762893845205</v>
+        <v>10.62006192369264</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>2</v>
       </c>
       <c r="K461" t="n">
-        <v>10.57521256310288</v>
+        <v>10.566399030751</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>2</v>
       </c>
       <c r="K462" t="n">
-        <v>10.53393775651718</v>
+        <v>10.53409753041523</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>2</v>
       </c>
       <c r="K463" t="n">
-        <v>10.43077548630827</v>
+        <v>10.43662746739787</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>2</v>
       </c>
       <c r="K464" t="n">
-        <v>10.43077548630827</v>
+        <v>10.43662746739787</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>2</v>
       </c>
       <c r="K465" t="n">
-        <v>10.42068784566052</v>
+        <v>10.42101067712413</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>2</v>
       </c>
       <c r="K466" t="n">
-        <v>10.42068784566052</v>
+        <v>10.42101067712413</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>2</v>
       </c>
       <c r="K467" t="n">
-        <v>10.41943348364486</v>
+        <v>10.42029336239018</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>2</v>
       </c>
       <c r="K468" t="n">
-        <v>10.35432902781823</v>
+        <v>10.35776478370159</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>2</v>
       </c>
       <c r="K469" t="n">
-        <v>10.34133630349838</v>
+        <v>10.33903140103864</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>2</v>
       </c>
       <c r="K470" t="n">
-        <v>10.21202816203017</v>
+        <v>10.21372758420196</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>2</v>
       </c>
       <c r="K471" t="n">
-        <v>10.21102951622582</v>
+        <v>10.20840278502609</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>2</v>
       </c>
       <c r="K472" t="n">
-        <v>10.21102951622582</v>
+        <v>10.20840278502609</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>2</v>
       </c>
       <c r="K473" t="n">
-        <v>10.22640886830701</v>
+        <v>10.21593983816498</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>2</v>
       </c>
       <c r="K474" t="n">
-        <v>10.25763427545448</v>
+        <v>10.2553655495469</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>2</v>
       </c>
       <c r="K475" t="n">
-        <v>10.28159798271222</v>
+        <v>10.27588320167188</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>2</v>
       </c>
       <c r="K476" t="n">
-        <v>10.44188854350157</v>
+        <v>10.44124841767497</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>2</v>
       </c>
       <c r="K477" t="n">
-        <v>10.47895692355912</v>
+        <v>10.47767363137753</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>2</v>
       </c>
       <c r="K478" t="n">
-        <v>10.50571926699294</v>
+        <v>10.50564830991744</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>2</v>
       </c>
       <c r="K479" t="n">
-        <v>10.55126557340915</v>
+        <v>10.55240333582531</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>2</v>
       </c>
       <c r="K480" t="n">
-        <v>10.5198503246035</v>
+        <v>10.53366274701672</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>2</v>
       </c>
       <c r="K481" t="n">
-        <v>10.48894429118816</v>
+        <v>10.48962438687562</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>2</v>
       </c>
       <c r="K482" t="n">
-        <v>10.4627099689811</v>
+        <v>10.46258700691156</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>2</v>
       </c>
       <c r="K483" t="n">
-        <v>10.42173243108309</v>
+        <v>10.4178235963323</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>2</v>
       </c>
       <c r="K484" t="n">
-        <v>10.35373897304834</v>
+        <v>10.34651584560387</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>2</v>
       </c>
       <c r="K485" t="n">
-        <v>10.31004676097293</v>
+        <v>10.30358033293316</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>2</v>
       </c>
       <c r="K486" t="n">
-        <v>10.28206646987647</v>
+        <v>10.28285456198714</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>2</v>
       </c>
       <c r="K487" t="n">
-        <v>10.27449948451268</v>
+        <v>10.26866659774177</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>2</v>
       </c>
       <c r="K488" t="n">
-        <v>10.21898950225064</v>
+        <v>10.2190399405957</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>2</v>
       </c>
       <c r="K489" t="n">
-        <v>10.25464799690077</v>
+        <v>10.25795725477807</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="K490" t="n">
-        <v>10.28552886964576</v>
+        <v>10.28561500906113</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>2</v>
       </c>
       <c r="K491" t="n">
-        <v>10.28552886964576</v>
+        <v>10.28561500906113</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>3</v>
       </c>
       <c r="K492" t="n">
-        <v>10.5605044281451</v>
+        <v>10.57414145576017</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>3</v>
       </c>
       <c r="K493" t="n">
-        <v>10.63779567365891</v>
+        <v>10.65108039725821</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>3</v>
       </c>
       <c r="K494" t="n">
-        <v>10.76752168148687</v>
+        <v>10.72715430937474</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>3</v>
       </c>
       <c r="K495" t="n">
-        <v>11.03001398611957</v>
+        <v>11.04420410476586</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>3</v>
       </c>
       <c r="K496" t="n">
-        <v>11.1214718244625</v>
+        <v>11.13879875891743</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>3</v>
       </c>
       <c r="K497" t="n">
-        <v>11.47080274197628</v>
+        <v>11.46723034815995</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>3</v>
       </c>
       <c r="K498" t="n">
-        <v>11.43886386260702</v>
+        <v>11.45318426309615</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>3</v>
       </c>
       <c r="K499" t="n">
-        <v>11.37962529499811</v>
+        <v>11.36976040724119</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>3</v>
       </c>
       <c r="K500" t="n">
-        <v>11.31918489037774</v>
+        <v>11.30840117971052</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>3</v>
       </c>
       <c r="K501" t="n">
-        <v>11.21287891830953</v>
+        <v>11.20540436314666</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>3</v>
       </c>
       <c r="K502" t="n">
-        <v>11.16729595488565</v>
+        <v>11.16728662016256</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>3</v>
       </c>
       <c r="K503" t="n">
-        <v>11.41722388221785</v>
+        <v>11.39928375337897</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>3</v>
       </c>
       <c r="K504" t="n">
-        <v>11.41722388221785</v>
+        <v>11.42862083587091</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>3</v>
       </c>
       <c r="K505" t="n">
-        <v>11.45696130914019</v>
+        <v>11.45694953831739</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>3</v>
       </c>
       <c r="K506" t="n">
-        <v>11.49924299742096</v>
+        <v>11.50268799024555</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>3</v>
       </c>
       <c r="K507" t="n">
-        <v>11.48244899014645</v>
+        <v>11.495545918824</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>3</v>
       </c>
       <c r="K508" t="n">
-        <v>11.3901381280884</v>
+        <v>11.38931510304857</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>3</v>
       </c>
       <c r="K509" t="n">
-        <v>11.37363983262314</v>
+        <v>11.36354682240322</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>3</v>
       </c>
       <c r="K510" t="n">
-        <v>11.28775805898583</v>
+        <v>11.28488446214915</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>3</v>
       </c>
       <c r="K511" t="n">
-        <v>11.22394076524176</v>
+        <v>11.2207688333475</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>3</v>
       </c>
       <c r="K512" t="n">
-        <v>11.22394076524176</v>
+        <v>11.2207688333475</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>3</v>
       </c>
       <c r="K513" t="n">
-        <v>11.23389839568448</v>
+        <v>11.22629888069298</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>3</v>
       </c>
       <c r="K514" t="n">
-        <v>11.27241230644776</v>
+        <v>11.27280116502349</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>3</v>
       </c>
       <c r="K515" t="n">
-        <v>11.32597863388344</v>
+        <v>11.3315583220291</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>3</v>
       </c>
       <c r="K516" t="n">
-        <v>11.38126810492651</v>
+        <v>11.38158570267749</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>3</v>
       </c>
       <c r="K517" t="n">
-        <v>11.41217026948235</v>
+        <v>11.41230089138574</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>3</v>
       </c>
       <c r="K518" t="n">
-        <v>11.43902807186389</v>
+        <v>11.42693968987601</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>3</v>
       </c>
       <c r="K519" t="n">
-        <v>11.49723062612045</v>
+        <v>11.49724353439781</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>3</v>
       </c>
       <c r="K520" t="n">
-        <v>11.49723062612045</v>
+        <v>11.49724353439781</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>3</v>
       </c>
       <c r="K521" t="n">
-        <v>11.57032127873344</v>
+        <v>11.55397675911058</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>3</v>
       </c>
       <c r="K522" t="n">
-        <v>11.63104098297971</v>
+        <v>11.64332920907385</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>3</v>
       </c>
       <c r="K523" t="n">
-        <v>11.76697637220648</v>
+        <v>11.76452174039836</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>3</v>
       </c>
       <c r="K524" t="n">
-        <v>11.82916115271758</v>
+        <v>11.82904045710544</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>3</v>
       </c>
       <c r="K525" t="n">
-        <v>12.05707892681302</v>
+        <v>12.05531380341291</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>3</v>
       </c>
       <c r="K526" t="n">
-        <v>12.06803513373314</v>
+        <v>12.07443183662029</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>3</v>
       </c>
       <c r="K527" t="n">
-        <v>12.04893169953036</v>
+        <v>12.04900582311851</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>3</v>
       </c>
       <c r="K528" t="n">
-        <v>12.0389550175544</v>
+        <v>12.03306892017002</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>3</v>
       </c>
       <c r="K529" t="n">
-        <v>11.998926980683</v>
+        <v>11.98983714100843</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>3</v>
       </c>
       <c r="K530" t="n">
-        <v>11.998926980683</v>
+        <v>11.98983714100843</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>3</v>
       </c>
       <c r="K531" t="n">
-        <v>11.82215042372483</v>
+        <v>11.8400170463852</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>3</v>
       </c>
       <c r="K532" t="n">
-        <v>11.81324904246243</v>
+        <v>11.80850689203026</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>3</v>
       </c>
       <c r="K533" t="n">
-        <v>11.79453945167533</v>
+        <v>11.79488436418689</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>3</v>
       </c>
       <c r="K534" t="n">
-        <v>11.7850053285351</v>
+        <v>11.79301729073942</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>3</v>
       </c>
       <c r="K535" t="n">
-        <v>11.76572251340087</v>
+        <v>11.76561265885427</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>3</v>
       </c>
       <c r="K536" t="n">
-        <v>11.67947608339587</v>
+        <v>11.70624508875017</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>3</v>
       </c>
       <c r="K537" t="n">
-        <v>11.65202052558358</v>
+        <v>11.63232965950649</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>3</v>
       </c>
       <c r="K538" t="n">
-        <v>11.59356194707989</v>
+        <v>11.59246572283907</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>3</v>
       </c>
       <c r="K539" t="n">
-        <v>11.59356194707989</v>
+        <v>11.59246572283907</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>3</v>
       </c>
       <c r="K540" t="n">
-        <v>11.42850437523201</v>
+        <v>11.42361754202225</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>3</v>
       </c>
       <c r="K541" t="n">
-        <v>11.31560120740596</v>
+        <v>11.33782714534496</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>3</v>
       </c>
       <c r="K542" t="n">
-        <v>11.27304572620665</v>
+        <v>11.27237843038574</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>3</v>
       </c>
       <c r="K543" t="n">
-        <v>11.25548189933456</v>
+        <v>11.24653935588317</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>3</v>
       </c>
       <c r="K544" t="n">
-        <v>11.17252211956091</v>
+        <v>11.17426861336533</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>3</v>
       </c>
       <c r="K545" t="n">
-        <v>11.15950510861468</v>
+        <v>11.14976217735916</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>3</v>
       </c>
       <c r="K546" t="n">
-        <v>10.91460342035283</v>
+        <v>10.91504051930327</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>3</v>
       </c>
       <c r="K547" t="n">
-        <v>10.8389084907314</v>
+        <v>10.84976641745249</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>3</v>
       </c>
       <c r="K548" t="n">
-        <v>10.76976577364041</v>
+        <v>10.77161443956318</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>3</v>
       </c>
       <c r="K549" t="n">
-        <v>10.71931982551673</v>
+        <v>10.71959446285154</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>3</v>
       </c>
       <c r="K550" t="n">
-        <v>10.65965156868274</v>
+        <v>10.65970274401597</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>3</v>
       </c>
       <c r="K551" t="n">
-        <v>10.65965156868274</v>
+        <v>10.65970274401597</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>3</v>
       </c>
       <c r="K552" t="n">
-        <v>10.56249862386659</v>
+        <v>10.55076166207</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>3</v>
       </c>
       <c r="K553" t="n">
-        <v>10.31099698398635</v>
+        <v>10.3659400376472</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>3</v>
       </c>
       <c r="K554" t="n">
-        <v>10.17704323231681</v>
+        <v>10.18122627595434</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>3</v>
       </c>
       <c r="K555" t="n">
-        <v>10.06308983475874</v>
+        <v>10.08171998048367</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>3</v>
       </c>
       <c r="K556" t="n">
-        <v>9.499178928218221</v>
+        <v>10.01088665804431</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>3</v>
       </c>
       <c r="K557" t="n">
-        <v>9.893991315762907</v>
+        <v>9.894439483436493</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>3</v>
       </c>
       <c r="K558" t="n">
-        <v>9.568595050769009</v>
+        <v>9.562848663075693</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>3</v>
       </c>
       <c r="K559" t="n">
-        <v>9.555616304161754</v>
+        <v>9.555679636702854</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>3</v>
       </c>
       <c r="K560" t="n">
-        <v>9.639782370996732</v>
+        <v>9.616505642034124</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>3</v>
       </c>
       <c r="K561" t="n">
-        <v>9.798528818629844</v>
+        <v>9.817588798115832</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>3</v>
       </c>
       <c r="K562" t="n">
-        <v>10.27119345472112</v>
+        <v>10.27026788973147</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>3</v>
       </c>
       <c r="K563" t="n">
-        <v>10.39367244020941</v>
+        <v>10.38917273611349</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>3</v>
       </c>
       <c r="K564" t="n">
-        <v>10.71463047245142</v>
+        <v>10.71055327370967</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>3</v>
       </c>
       <c r="K565" t="n">
-        <v>10.99594007752292</v>
+        <v>11.00328651246747</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>3</v>
       </c>
       <c r="K566" t="n">
-        <v>11.0172558245213</v>
+        <v>11.0170556018353</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>3</v>
       </c>
       <c r="K567" t="n">
-        <v>11.04024322318195</v>
+        <v>11.04224409880645</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>3</v>
       </c>
       <c r="K568" t="n">
-        <v>11.03849699928122</v>
+        <v>11.03864673768601</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>3</v>
       </c>
       <c r="K569" t="n">
-        <v>10.97151367959733</v>
+        <v>10.99166609962692</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>3</v>
       </c>
       <c r="K570" t="n">
-        <v>10.97151367959733</v>
+        <v>10.95854618913873</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>3</v>
       </c>
       <c r="K571" t="n">
-        <v>10.97151367959733</v>
+        <v>10.95854618913873</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>3</v>
       </c>
       <c r="K572" t="n">
-        <v>10.82394916999146</v>
+        <v>10.82003658769223</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>3</v>
       </c>
       <c r="K573" t="n">
-        <v>10.78939397467837</v>
+        <v>10.79528201112706</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>3</v>
       </c>
       <c r="K574" t="n">
-        <v>10.71313331175407</v>
+        <v>10.71399933283572</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>3</v>
       </c>
       <c r="K575" t="n">
-        <v>10.71313331175407</v>
+        <v>10.71399933283572</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>3</v>
       </c>
       <c r="K576" t="n">
-        <v>10.55267718055324</v>
+        <v>10.52730478064049</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>3</v>
       </c>
       <c r="K577" t="n">
-        <v>10.55267718055324</v>
+        <v>10.52730478064049</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>3</v>
       </c>
       <c r="K578" t="n">
-        <v>10.37098073603054</v>
+        <v>10.36863629622487</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>3</v>
       </c>
       <c r="K579" t="n">
-        <v>10.37098073603054</v>
+        <v>10.36863629622487</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>3</v>
       </c>
       <c r="K580" t="n">
-        <v>10.34114649536104</v>
+        <v>10.31541861873759</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>3</v>
       </c>
       <c r="K581" t="n">
-        <v>10.24748949666953</v>
+        <v>10.26763626472932</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>3</v>
       </c>
       <c r="K582" t="n">
-        <v>10.23669867735184</v>
+        <v>10.23495384877388</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>3</v>
       </c>
       <c r="K583" t="n">
-        <v>10.27147440982161</v>
+        <v>10.25173135008557</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>3</v>
       </c>
       <c r="K584" t="n">
-        <v>10.62964715009147</v>
+        <v>10.62121119630592</v>
       </c>
     </row>
     <row r="585">
@@ -24426,7 +24426,7 @@
         <v>3</v>
       </c>
       <c r="K585" t="n">
-        <v>10.88494954707124</v>
+        <v>10.90764040234234</v>
       </c>
     </row>
     <row r="586">
@@ -24467,7 +24467,7 @@
         <v>3</v>
       </c>
       <c r="K586" t="n">
-        <v>10.96505400849741</v>
+        <v>10.96393799637345</v>
       </c>
     </row>
     <row r="587">
@@ -24508,7 +24508,7 @@
         <v>3</v>
       </c>
       <c r="K587" t="n">
-        <v>11.01859052850092</v>
+        <v>11.04557045894274</v>
       </c>
     </row>
     <row r="588">
@@ -24549,7 +24549,7 @@
         <v>3</v>
       </c>
       <c r="K588" t="n">
-        <v>11.01859052850092</v>
+        <v>11.04557045894274</v>
       </c>
     </row>
     <row r="589">
@@ -24590,7 +24590,7 @@
         <v>3</v>
       </c>
       <c r="K589" t="n">
-        <v>11.50709574335611</v>
+        <v>11.50438865670532</v>
       </c>
     </row>
     <row r="590">
@@ -24631,7 +24631,7 @@
         <v>3</v>
       </c>
       <c r="K590" t="n">
-        <v>11.61469189890569</v>
+        <v>11.59393160809646</v>
       </c>
     </row>
     <row r="591">
@@ -24672,7 +24672,7 @@
         <v>3</v>
       </c>
       <c r="K591" t="n">
-        <v>11.71011651341954</v>
+        <v>11.70992457918919</v>
       </c>
     </row>
     <row r="592">
@@ -24713,7 +24713,7 @@
         <v>3</v>
       </c>
       <c r="K592" t="n">
-        <v>11.80025499857418</v>
+        <v>11.81730677603188</v>
       </c>
     </row>
     <row r="593">
@@ -24754,7 +24754,7 @@
         <v>3</v>
       </c>
       <c r="K593" t="n">
-        <v>11.85336730558675</v>
+        <v>11.85315275788222</v>
       </c>
     </row>
     <row r="594">
@@ -24795,7 +24795,7 @@
         <v>3</v>
       </c>
       <c r="K594" t="n">
-        <v>11.97529660171574</v>
+        <v>11.98212335782301</v>
       </c>
     </row>
     <row r="595">
@@ -24836,7 +24836,7 @@
         <v>3</v>
       </c>
       <c r="K595" t="n">
-        <v>12.03406867451463</v>
+        <v>12.04017374846207</v>
       </c>
     </row>
     <row r="596">
@@ -24877,7 +24877,7 @@
         <v>3</v>
       </c>
       <c r="K596" t="n">
-        <v>12.04909631743753</v>
+        <v>12.04937382052078</v>
       </c>
     </row>
     <row r="597">
@@ -24918,7 +24918,7 @@
         <v>3</v>
       </c>
       <c r="K597" t="n">
-        <v>12.0610019084676</v>
+        <v>12.05817404164377</v>
       </c>
     </row>
     <row r="598">
@@ -24959,7 +24959,7 @@
         <v>3</v>
       </c>
       <c r="K598" t="n">
-        <v>12.0610019084676</v>
+        <v>12.05817404164377</v>
       </c>
     </row>
     <row r="599">
@@ -25000,7 +25000,7 @@
         <v>3</v>
       </c>
       <c r="K599" t="n">
-        <v>12.0610019084676</v>
+        <v>12.05817404164377</v>
       </c>
     </row>
     <row r="600">
@@ -25041,7 +25041,7 @@
         <v>3</v>
       </c>
       <c r="K600" t="n">
-        <v>11.98533633789375</v>
+        <v>11.97755468673577</v>
       </c>
     </row>
     <row r="601">
@@ -25082,7 +25082,7 @@
         <v>3</v>
       </c>
       <c r="K601" t="n">
-        <v>11.95875842211126</v>
+        <v>11.95904425436913</v>
       </c>
     </row>
     <row r="602">
@@ -25123,7 +25123,7 @@
         <v>3</v>
       </c>
       <c r="K602" t="n">
-        <v>11.95332745778167</v>
+        <v>11.95549068567392</v>
       </c>
     </row>
     <row r="603">
@@ -25164,7 +25164,7 @@
         <v>3</v>
       </c>
       <c r="K603" t="n">
-        <v>11.75052131732721</v>
+        <v>11.75283733265084</v>
       </c>
     </row>
     <row r="604">
@@ -25205,7 +25205,7 @@
         <v>3</v>
       </c>
       <c r="K604" t="n">
-        <v>11.67023804085437</v>
+        <v>11.67085275067225</v>
       </c>
     </row>
     <row r="605">
@@ -25246,7 +25246,7 @@
         <v>3</v>
       </c>
       <c r="K605" t="n">
-        <v>11.67025584813771</v>
+        <v>11.67050674436456</v>
       </c>
     </row>
     <row r="606">
@@ -25287,7 +25287,7 @@
         <v>3</v>
       </c>
       <c r="K606" t="n">
-        <v>11.66314335145914</v>
+        <v>11.66657213222794</v>
       </c>
     </row>
     <row r="607">
@@ -25328,7 +25328,7 @@
         <v>3</v>
       </c>
       <c r="K607" t="n">
-        <v>11.40169047317085</v>
+        <v>11.40179767165283</v>
       </c>
     </row>
     <row r="608">
@@ -25369,7 +25369,7 @@
         <v>3</v>
       </c>
       <c r="K608" t="n">
-        <v>11.31718438534254</v>
+        <v>11.30058864789203</v>
       </c>
     </row>
     <row r="609">
@@ -25410,7 +25410,7 @@
         <v>3</v>
       </c>
       <c r="K609" t="n">
-        <v>11.13341112188706</v>
+        <v>11.13810967757812</v>
       </c>
     </row>
     <row r="610">
@@ -25451,7 +25451,7 @@
         <v>3</v>
       </c>
       <c r="K610" t="n">
-        <v>11.13341112188706</v>
+        <v>11.13810967757812</v>
       </c>
     </row>
     <row r="611">
@@ -25492,7 +25492,7 @@
         <v>3</v>
       </c>
       <c r="K611" t="n">
-        <v>11.01598286174307</v>
+        <v>11.01614718577043</v>
       </c>
     </row>
     <row r="612">
@@ -25533,7 +25533,7 @@
         <v>3</v>
       </c>
       <c r="K612" t="n">
-        <v>10.87881078909192</v>
+        <v>10.88339296181535</v>
       </c>
     </row>
     <row r="613">
@@ -25574,7 +25574,7 @@
         <v>3</v>
       </c>
       <c r="K613" t="n">
-        <v>10.63941080838967</v>
+        <v>10.6323517342487</v>
       </c>
     </row>
     <row r="614">
@@ -25615,7 +25615,7 @@
         <v>3</v>
       </c>
       <c r="K614" t="n">
-        <v>10.61353213487807</v>
+        <v>10.61996694513668</v>
       </c>
     </row>
     <row r="615">
@@ -25656,7 +25656,7 @@
         <v>3</v>
       </c>
       <c r="K615" t="n">
-        <v>10.61116792971439</v>
+        <v>10.61839589272268</v>
       </c>
     </row>
     <row r="616">
@@ -25697,7 +25697,7 @@
         <v>3</v>
       </c>
       <c r="K616" t="n">
-        <v>10.58312858705997</v>
+        <v>10.59560748295024</v>
       </c>
     </row>
     <row r="617">
@@ -25738,7 +25738,7 @@
         <v>3</v>
       </c>
       <c r="K617" t="n">
-        <v>10.58312858705997</v>
+        <v>10.59560748295024</v>
       </c>
     </row>
     <row r="618">
@@ -25779,7 +25779,7 @@
         <v>3</v>
       </c>
       <c r="K618" t="n">
-        <v>10.55339928939033</v>
+        <v>10.54474570693663</v>
       </c>
     </row>
     <row r="619">
@@ -25820,7 +25820,7 @@
         <v>3</v>
       </c>
       <c r="K619" t="n">
-        <v>10.55339928939033</v>
+        <v>10.54474570693663</v>
       </c>
     </row>
     <row r="620">
@@ -25861,7 +25861,7 @@
         <v>3</v>
       </c>
       <c r="K620" t="n">
-        <v>10.50330085656178</v>
+        <v>10.50285150497022</v>
       </c>
     </row>
     <row r="621">
@@ -25902,7 +25902,7 @@
         <v>3</v>
       </c>
       <c r="K621" t="n">
-        <v>10.57457962324112</v>
+        <v>10.57113354707552</v>
       </c>
     </row>
     <row r="622">
@@ -25943,7 +25943,7 @@
         <v>3</v>
       </c>
       <c r="K622" t="n">
-        <v>10.97992279853422</v>
+        <v>10.91761367758605</v>
       </c>
     </row>
     <row r="623">
@@ -25984,7 +25984,7 @@
         <v>3</v>
       </c>
       <c r="K623" t="n">
-        <v>11.21520920242776</v>
+        <v>11.25395142846657</v>
       </c>
     </row>
     <row r="624">
@@ -26025,7 +26025,7 @@
         <v>3</v>
       </c>
       <c r="K624" t="n">
-        <v>11.74721912560212</v>
+        <v>11.70409034929491</v>
       </c>
     </row>
     <row r="625">
@@ -26066,7 +26066,7 @@
         <v>3</v>
       </c>
       <c r="K625" t="n">
-        <v>11.81556929724159</v>
+        <v>11.81306785451972</v>
       </c>
     </row>
     <row r="626">
@@ -26107,7 +26107,7 @@
         <v>3</v>
       </c>
       <c r="K626" t="n">
-        <v>11.83662593272055</v>
+        <v>11.83235113172312</v>
       </c>
     </row>
     <row r="627">
@@ -26148,7 +26148,7 @@
         <v>3</v>
       </c>
       <c r="K627" t="n">
-        <v>11.77486205625053</v>
+        <v>11.75673748585578</v>
       </c>
     </row>
     <row r="628">
@@ -26189,7 +26189,7 @@
         <v>3</v>
       </c>
       <c r="K628" t="n">
-        <v>11.77486205625053</v>
+        <v>11.75673748585578</v>
       </c>
     </row>
     <row r="629">
@@ -26230,7 +26230,7 @@
         <v>3</v>
       </c>
       <c r="K629" t="n">
-        <v>11.52966617031475</v>
+        <v>11.56978612577751</v>
       </c>
     </row>
     <row r="630">
@@ -26271,7 +26271,7 @@
         <v>3</v>
       </c>
       <c r="K630" t="n">
-        <v>11.34517880299425</v>
+        <v>11.33503422411541</v>
       </c>
     </row>
     <row r="631">
@@ -26312,7 +26312,7 @@
         <v>3</v>
       </c>
       <c r="K631" t="n">
-        <v>11.31761287483948</v>
+        <v>11.31764813305419</v>
       </c>
     </row>
     <row r="632">
@@ -26353,7 +26353,7 @@
         <v>3</v>
       </c>
       <c r="K632" t="n">
-        <v>11.19597414206966</v>
+        <v>11.20099421977675</v>
       </c>
     </row>
     <row r="633">
@@ -26394,7 +26394,7 @@
         <v>3</v>
       </c>
       <c r="K633" t="n">
-        <v>11.15915700841892</v>
+        <v>11.15139522805555</v>
       </c>
     </row>
     <row r="634">
@@ -26435,7 +26435,7 @@
         <v>3</v>
       </c>
       <c r="K634" t="n">
-        <v>11.14450268808417</v>
+        <v>11.13993371143347</v>
       </c>
     </row>
     <row r="635">
@@ -26476,7 +26476,7 @@
         <v>3</v>
       </c>
       <c r="K635" t="n">
-        <v>11.13374875560288</v>
+        <v>11.09712635698517</v>
       </c>
     </row>
     <row r="636">
@@ -26517,7 +26517,7 @@
         <v>3</v>
       </c>
       <c r="K636" t="n">
-        <v>11.11796447479111</v>
+        <v>11.10849124212842</v>
       </c>
     </row>
     <row r="637">
@@ -26558,7 +26558,7 @@
         <v>3</v>
       </c>
       <c r="K637" t="n">
-        <v>11.10166705370158</v>
+        <v>11.09215911613767</v>
       </c>
     </row>
     <row r="638">
@@ -26599,7 +26599,7 @@
         <v>3</v>
       </c>
       <c r="K638" t="n">
-        <v>11.13539239993056</v>
+        <v>11.13550458167024</v>
       </c>
     </row>
     <row r="639">
@@ -26640,7 +26640,7 @@
         <v>3</v>
       </c>
       <c r="K639" t="n">
-        <v>11.23061094143682</v>
+        <v>11.22570044305128</v>
       </c>
     </row>
     <row r="640">
@@ -26681,7 +26681,7 @@
         <v>3</v>
       </c>
       <c r="K640" t="n">
-        <v>11.23061094143682</v>
+        <v>11.22570044305128</v>
       </c>
     </row>
     <row r="641">
@@ -26722,7 +26722,7 @@
         <v>3</v>
       </c>
       <c r="K641" t="n">
-        <v>11.35267198465505</v>
+        <v>11.35082033724568</v>
       </c>
     </row>
     <row r="642">
@@ -26763,7 +26763,7 @@
         <v>3</v>
       </c>
       <c r="K642" t="n">
-        <v>11.35267198465505</v>
+        <v>11.34194052818677</v>
       </c>
     </row>
     <row r="643">
@@ -26804,7 +26804,7 @@
         <v>3</v>
       </c>
       <c r="K643" t="n">
-        <v>11.35267198465505</v>
+        <v>11.34194052818677</v>
       </c>
     </row>
     <row r="644">
@@ -26845,7 +26845,7 @@
         <v>3</v>
       </c>
       <c r="K644" t="n">
-        <v>11.29252982864427</v>
+        <v>11.29363525794221</v>
       </c>
     </row>
     <row r="645">
@@ -26886,7 +26886,7 @@
         <v>3</v>
       </c>
       <c r="K645" t="n">
-        <v>11.27801765337281</v>
+        <v>11.26639842694359</v>
       </c>
     </row>
     <row r="646">
@@ -26927,7 +26927,7 @@
         <v>3</v>
       </c>
       <c r="K646" t="n">
-        <v>11.15190493313474</v>
+        <v>11.13509867484441</v>
       </c>
     </row>
     <row r="647">
@@ -26968,7 +26968,7 @@
         <v>3</v>
       </c>
       <c r="K647" t="n">
-        <v>11.15190493313474</v>
+        <v>11.13509867484441</v>
       </c>
     </row>
     <row r="648">
@@ -27009,7 +27009,7 @@
         <v>3</v>
       </c>
       <c r="K648" t="n">
-        <v>11.08390961690373</v>
+        <v>11.07124048680137</v>
       </c>
     </row>
     <row r="649">
@@ -27050,7 +27050,7 @@
         <v>3</v>
       </c>
       <c r="K649" t="n">
-        <v>11.04009575755981</v>
+        <v>11.03355078130118</v>
       </c>
     </row>
     <row r="650">
@@ -27091,7 +27091,7 @@
         <v>3</v>
       </c>
       <c r="K650" t="n">
-        <v>10.98684308625631</v>
+        <v>10.98810138663254</v>
       </c>
     </row>
     <row r="651">
@@ -27132,7 +27132,7 @@
         <v>3</v>
       </c>
       <c r="K651" t="n">
-        <v>10.93917919940125</v>
+        <v>10.94477291344445</v>
       </c>
     </row>
     <row r="652">
@@ -27173,7 +27173,7 @@
         <v>3</v>
       </c>
       <c r="K652" t="n">
-        <v>11.08055702692947</v>
+        <v>11.09420106438755</v>
       </c>
     </row>
     <row r="653">
@@ -27214,7 +27214,7 @@
         <v>3</v>
       </c>
       <c r="K653" t="n">
-        <v>11.11540670036686</v>
+        <v>11.11532652286613</v>
       </c>
     </row>
     <row r="654">
@@ -27255,7 +27255,7 @@
         <v>3</v>
       </c>
       <c r="K654" t="n">
-        <v>11.47363227974835</v>
+        <v>11.474201568454</v>
       </c>
     </row>
     <row r="655">
@@ -27296,7 +27296,7 @@
         <v>3</v>
       </c>
       <c r="K655" t="n">
-        <v>11.60487582108698</v>
+        <v>11.57435667946015</v>
       </c>
     </row>
     <row r="656">
@@ -27337,7 +27337,7 @@
         <v>3</v>
       </c>
       <c r="K656" t="n">
-        <v>11.65684290029081</v>
+        <v>11.62461361049229</v>
       </c>
     </row>
     <row r="657">
@@ -27378,7 +27378,7 @@
         <v>3</v>
       </c>
       <c r="K657" t="n">
-        <v>11.8530050830401</v>
+        <v>11.8433833397625</v>
       </c>
     </row>
     <row r="658">
@@ -27419,7 +27419,7 @@
         <v>3</v>
       </c>
       <c r="K658" t="n">
-        <v>11.8530050830401</v>
+        <v>11.8433833397625</v>
       </c>
     </row>
     <row r="659">
@@ -27460,7 +27460,7 @@
         <v>3</v>
       </c>
       <c r="K659" t="n">
-        <v>11.8792887497335</v>
+        <v>11.87420153266861</v>
       </c>
     </row>
     <row r="660">
@@ -27501,7 +27501,7 @@
         <v>3</v>
       </c>
       <c r="K660" t="n">
-        <v>11.90878944726344</v>
+        <v>11.90842864230036</v>
       </c>
     </row>
     <row r="661">
@@ -27542,7 +27542,7 @@
         <v>3</v>
       </c>
       <c r="K661" t="n">
-        <v>11.97756267572801</v>
+        <v>11.98375874404254</v>
       </c>
     </row>
     <row r="662">
@@ -27583,7 +27583,7 @@
         <v>3</v>
       </c>
       <c r="K662" t="n">
-        <v>12.08379256634418</v>
+        <v>12.0611646609095</v>
       </c>
     </row>
     <row r="663">
@@ -27624,7 +27624,7 @@
         <v>3</v>
       </c>
       <c r="K663" t="n">
-        <v>12.32465867395338</v>
+        <v>12.34185339250128</v>
       </c>
     </row>
     <row r="664">
@@ -27665,7 +27665,7 @@
         <v>3</v>
       </c>
       <c r="K664" t="n">
-        <v>12.41972764285574</v>
+        <v>12.41975434336221</v>
       </c>
     </row>
     <row r="665">
@@ -27706,7 +27706,7 @@
         <v>3</v>
       </c>
       <c r="K665" t="n">
-        <v>12.42159424534634</v>
+        <v>12.42089734076201</v>
       </c>
     </row>
     <row r="666">
@@ -27747,7 +27747,7 @@
         <v>3</v>
       </c>
       <c r="K666" t="n">
-        <v>12.44040109115974</v>
+        <v>12.43331824829957</v>
       </c>
     </row>
     <row r="667">
@@ -27788,7 +27788,7 @@
         <v>3</v>
       </c>
       <c r="K667" t="n">
-        <v>12.31499693452924</v>
+        <v>12.30307264716587</v>
       </c>
     </row>
     <row r="668">
@@ -27829,7 +27829,7 @@
         <v>3</v>
       </c>
       <c r="K668" t="n">
-        <v>12.25086239392128</v>
+        <v>12.2758822371203</v>
       </c>
     </row>
     <row r="669">
@@ -27870,7 +27870,7 @@
         <v>3</v>
       </c>
       <c r="K669" t="n">
-        <v>11.94669532851258</v>
+        <v>11.95132559503083</v>
       </c>
     </row>
     <row r="670">
@@ -27911,7 +27911,7 @@
         <v>3</v>
       </c>
       <c r="K670" t="n">
-        <v>11.84072545287372</v>
+        <v>11.84065711443872</v>
       </c>
     </row>
     <row r="671">
@@ -27952,7 +27952,7 @@
         <v>3</v>
       </c>
       <c r="K671" t="n">
-        <v>11.59226546830381</v>
+        <v>11.59224737100755</v>
       </c>
     </row>
     <row r="672">
@@ -27993,7 +27993,7 @@
         <v>3</v>
       </c>
       <c r="K672" t="n">
-        <v>11.52193829653693</v>
+        <v>11.52292577259936</v>
       </c>
     </row>
     <row r="673">
@@ -28034,7 +28034,7 @@
         <v>3</v>
       </c>
       <c r="K673" t="n">
-        <v>11.49950886057819</v>
+        <v>11.50867492320384</v>
       </c>
     </row>
     <row r="674">
@@ -28075,7 +28075,7 @@
         <v>3</v>
       </c>
       <c r="K674" t="n">
-        <v>11.41665186882516</v>
+        <v>11.40998700838814</v>
       </c>
     </row>
     <row r="675">
@@ -28116,7 +28116,7 @@
         <v>3</v>
       </c>
       <c r="K675" t="n">
-        <v>11.36409432155552</v>
+        <v>11.36095156522753</v>
       </c>
     </row>
     <row r="676">
@@ -28157,7 +28157,7 @@
         <v>3</v>
       </c>
       <c r="K676" t="n">
-        <v>11.38225744611824</v>
+        <v>11.39035483308634</v>
       </c>
     </row>
     <row r="677">
@@ -28198,7 +28198,7 @@
         <v>3</v>
       </c>
       <c r="K677" t="n">
-        <v>11.51798820699751</v>
+        <v>11.51201711563074</v>
       </c>
     </row>
     <row r="678">
@@ -28239,7 +28239,7 @@
         <v>3</v>
       </c>
       <c r="K678" t="n">
-        <v>11.51798820699751</v>
+        <v>11.51201711563074</v>
       </c>
     </row>
     <row r="679">
@@ -28280,7 +28280,7 @@
         <v>3</v>
       </c>
       <c r="K679" t="n">
-        <v>11.74641179607546</v>
+        <v>11.77977663027225</v>
       </c>
     </row>
     <row r="680">
@@ -28321,7 +28321,7 @@
         <v>3</v>
       </c>
       <c r="K680" t="n">
-        <v>11.74641179607546</v>
+        <v>11.77977663027225</v>
       </c>
     </row>
     <row r="681">
@@ -28362,7 +28362,7 @@
         <v>3</v>
       </c>
       <c r="K681" t="n">
-        <v>11.74641179607546</v>
+        <v>11.77977663027225</v>
       </c>
     </row>
     <row r="682">
@@ -28403,7 +28403,7 @@
         <v>3</v>
       </c>
       <c r="K682" t="n">
-        <v>12.13815706066337</v>
+        <v>12.12324577385282</v>
       </c>
     </row>
     <row r="683">
@@ -28444,7 +28444,7 @@
         <v>3</v>
       </c>
       <c r="K683" t="n">
-        <v>12.38991711818515</v>
+        <v>12.39630188987187</v>
       </c>
     </row>
     <row r="684">
@@ -28485,7 +28485,7 @@
         <v>3</v>
       </c>
       <c r="K684" t="n">
-        <v>12.38991711818515</v>
+        <v>12.39630188987187</v>
       </c>
     </row>
     <row r="685">
@@ -28526,7 +28526,7 @@
         <v>3</v>
       </c>
       <c r="K685" t="n">
-        <v>12.40595419185324</v>
+        <v>12.4045954262689</v>
       </c>
     </row>
     <row r="686">
@@ -28567,7 +28567,7 @@
         <v>3</v>
       </c>
       <c r="K686" t="n">
-        <v>12.36860816319219</v>
+        <v>12.36817370154916</v>
       </c>
     </row>
     <row r="687">
@@ -28608,7 +28608,7 @@
         <v>3</v>
       </c>
       <c r="K687" t="n">
-        <v>12.30545236749803</v>
+        <v>12.30507381213876</v>
       </c>
     </row>
     <row r="688">
@@ -28649,7 +28649,7 @@
         <v>3</v>
       </c>
       <c r="K688" t="n">
-        <v>12.19021363432149</v>
+        <v>12.18907854453369</v>
       </c>
     </row>
     <row r="689">
@@ -28690,7 +28690,7 @@
         <v>3</v>
       </c>
       <c r="K689" t="n">
-        <v>12.12349668410686</v>
+        <v>12.09162147299834</v>
       </c>
     </row>
     <row r="690">
@@ -28731,7 +28731,7 @@
         <v>3</v>
       </c>
       <c r="K690" t="n">
-        <v>11.89041516098447</v>
+        <v>11.8911798924836</v>
       </c>
     </row>
     <row r="691">
@@ -28772,7 +28772,7 @@
         <v>3</v>
       </c>
       <c r="K691" t="n">
-        <v>11.66173114750614</v>
+        <v>11.616744726994</v>
       </c>
     </row>
     <row r="692">
@@ -28813,7 +28813,7 @@
         <v>3</v>
       </c>
       <c r="K692" t="n">
-        <v>11.66173114750614</v>
+        <v>11.616744726994</v>
       </c>
     </row>
     <row r="693">
@@ -28854,7 +28854,7 @@
         <v>3</v>
       </c>
       <c r="K693" t="n">
-        <v>11.4993561537757</v>
+        <v>11.45364487369717</v>
       </c>
     </row>
     <row r="694">
@@ -28895,7 +28895,7 @@
         <v>3</v>
       </c>
       <c r="K694" t="n">
-        <v>11.4993561537757</v>
+        <v>11.45364487369717</v>
       </c>
     </row>
     <row r="695">
@@ -28936,7 +28936,7 @@
         <v>3</v>
       </c>
       <c r="K695" t="n">
-        <v>11.32144772168793</v>
+        <v>11.3464162809651</v>
       </c>
     </row>
     <row r="696">
@@ -28977,7 +28977,7 @@
         <v>3</v>
       </c>
       <c r="K696" t="n">
-        <v>11.32144772168793</v>
+        <v>11.3464162809651</v>
       </c>
     </row>
     <row r="697">
@@ -29018,7 +29018,7 @@
         <v>3</v>
       </c>
       <c r="K697" t="n">
-        <v>11.31284911860159</v>
+        <v>11.31571932577233</v>
       </c>
     </row>
     <row r="698">
@@ -29059,7 +29059,7 @@
         <v>3</v>
       </c>
       <c r="K698" t="n">
-        <v>11.67827517214235</v>
+        <v>11.67868157583687</v>
       </c>
     </row>
     <row r="699">
@@ -29100,7 +29100,7 @@
         <v>3</v>
       </c>
       <c r="K699" t="n">
-        <v>11.80712858145534</v>
+        <v>11.76602828401343</v>
       </c>
     </row>
     <row r="700">
@@ -29141,7 +29141,7 @@
         <v>3</v>
       </c>
       <c r="K700" t="n">
-        <v>12.0925445877319</v>
+        <v>12.09053056758984</v>
       </c>
     </row>
     <row r="701">
@@ -29182,7 +29182,7 @@
         <v>3</v>
       </c>
       <c r="K701" t="n">
-        <v>12.08535272974469</v>
+        <v>12.09012050469386</v>
       </c>
     </row>
     <row r="702">
@@ -29223,7 +29223,7 @@
         <v>3</v>
       </c>
       <c r="K702" t="n">
-        <v>12.04307521421531</v>
+        <v>12.03716191554282</v>
       </c>
     </row>
     <row r="703">
@@ -29264,7 +29264,7 @@
         <v>3</v>
       </c>
       <c r="K703" t="n">
-        <v>11.94611684354262</v>
+        <v>11.94602017758141</v>
       </c>
     </row>
     <row r="704">
@@ -29305,7 +29305,7 @@
         <v>3</v>
       </c>
       <c r="K704" t="n">
-        <v>11.93221631196808</v>
+        <v>11.92511394871624</v>
       </c>
     </row>
     <row r="705">
@@ -29346,7 +29346,7 @@
         <v>3</v>
       </c>
       <c r="K705" t="n">
-        <v>11.96782381310601</v>
+        <v>11.98197007392296</v>
       </c>
     </row>
     <row r="706">
@@ -29387,7 +29387,7 @@
         <v>3</v>
       </c>
       <c r="K706" t="n">
-        <v>12.08517482572628</v>
+        <v>12.09903070806026</v>
       </c>
     </row>
     <row r="707">
@@ -29428,7 +29428,7 @@
         <v>3</v>
       </c>
       <c r="K707" t="n">
-        <v>12.12701742195646</v>
+        <v>12.12100815664865</v>
       </c>
     </row>
     <row r="708">
@@ -29469,7 +29469,7 @@
         <v>3</v>
       </c>
       <c r="K708" t="n">
-        <v>12.12701742195646</v>
+        <v>12.12100815664865</v>
       </c>
     </row>
     <row r="709">
@@ -29510,7 +29510,7 @@
         <v>3</v>
       </c>
       <c r="K709" t="n">
-        <v>12.12701742195646</v>
+        <v>12.12100815664865</v>
       </c>
     </row>
     <row r="710">
@@ -29551,7 +29551,7 @@
         <v>3</v>
       </c>
       <c r="K710" t="n">
-        <v>12.20251822580295</v>
+        <v>12.20933635259386</v>
       </c>
     </row>
     <row r="711">
@@ -29592,7 +29592,7 @@
         <v>3</v>
       </c>
       <c r="K711" t="n">
-        <v>12.24171941738657</v>
+        <v>12.2547049390001</v>
       </c>
     </row>
     <row r="712">
@@ -29633,7 +29633,7 @@
         <v>3</v>
       </c>
       <c r="K712" t="n">
-        <v>12.31394120283852</v>
+        <v>12.33371956943482</v>
       </c>
     </row>
     <row r="713">
@@ -29674,7 +29674,7 @@
         <v>3</v>
       </c>
       <c r="K713" t="n">
-        <v>12.53928339721439</v>
+        <v>12.53954425227726</v>
       </c>
     </row>
     <row r="714">
@@ -29715,7 +29715,7 @@
         <v>3</v>
       </c>
       <c r="K714" t="n">
-        <v>12.55418054239263</v>
+        <v>12.54955888191316</v>
       </c>
     </row>
     <row r="715">
@@ -29756,7 +29756,7 @@
         <v>3</v>
       </c>
       <c r="K715" t="n">
-        <v>12.63218384861915</v>
+        <v>12.63710184784906</v>
       </c>
     </row>
     <row r="716">
@@ -29797,7 +29797,7 @@
         <v>3</v>
       </c>
       <c r="K716" t="n">
-        <v>12.47741125749183</v>
+        <v>12.48293064777634</v>
       </c>
     </row>
     <row r="717">
@@ -29838,7 +29838,7 @@
         <v>3</v>
       </c>
       <c r="K717" t="n">
-        <v>12.4314590597138</v>
+        <v>12.39242671936847</v>
       </c>
     </row>
     <row r="718">
@@ -29879,7 +29879,7 @@
         <v>3</v>
       </c>
       <c r="K718" t="n">
-        <v>12.34630416434628</v>
+        <v>12.34607905185371</v>
       </c>
     </row>
     <row r="719">
@@ -29920,7 +29920,7 @@
         <v>3</v>
       </c>
       <c r="K719" t="n">
-        <v>12.21034578383303</v>
+        <v>12.24964661013858</v>
       </c>
     </row>
     <row r="720">
@@ -29961,7 +29961,7 @@
         <v>3</v>
       </c>
       <c r="K720" t="n">
-        <v>12.00471930003101</v>
+        <v>11.9964331862894</v>
       </c>
     </row>
     <row r="721">
@@ -30002,7 +30002,7 @@
         <v>3</v>
       </c>
       <c r="K721" t="n">
-        <v>12.00471930003101</v>
+        <v>11.9964331862894</v>
       </c>
     </row>
     <row r="722">
@@ -30043,7 +30043,7 @@
         <v>3</v>
       </c>
       <c r="K722" t="n">
-        <v>12.33248914027268</v>
+        <v>12.30448874992519</v>
       </c>
     </row>
     <row r="723">
@@ -30084,7 +30084,7 @@
         <v>3</v>
       </c>
       <c r="K723" t="n">
-        <v>12.38763148998822</v>
+        <v>12.39937577377943</v>
       </c>
     </row>
     <row r="724">
@@ -30125,7 +30125,7 @@
         <v>3</v>
       </c>
       <c r="K724" t="n">
-        <v>12.59652520082949</v>
+        <v>12.59649734491144</v>
       </c>
     </row>
     <row r="725">
@@ -30166,7 +30166,7 @@
         <v>3</v>
       </c>
       <c r="K725" t="n">
-        <v>12.67891416342733</v>
+        <v>12.65434932422174</v>
       </c>
     </row>
     <row r="726">
@@ -30207,7 +30207,7 @@
         <v>3</v>
       </c>
       <c r="K726" t="n">
-        <v>12.75765116160032</v>
+        <v>12.75765658832074</v>
       </c>
     </row>
     <row r="727">
@@ -30248,7 +30248,7 @@
         <v>3</v>
       </c>
       <c r="K727" t="n">
-        <v>12.83575213275787</v>
+        <v>12.8393761017376</v>
       </c>
     </row>
     <row r="728">
@@ -30289,7 +30289,7 @@
         <v>3</v>
       </c>
       <c r="K728" t="n">
-        <v>12.61929211090303</v>
+        <v>12.61931365387126</v>
       </c>
     </row>
     <row r="729">
@@ -30330,7 +30330,7 @@
         <v>3</v>
       </c>
       <c r="K729" t="n">
-        <v>12.17436392202604</v>
+        <v>12.21320940965592</v>
       </c>
     </row>
     <row r="730">
@@ -30371,7 +30371,7 @@
         <v>3</v>
       </c>
       <c r="K730" t="n">
-        <v>12.17436392202604</v>
+        <v>12.174549504009</v>
       </c>
     </row>
     <row r="731">
@@ -30412,7 +30412,7 @@
         <v>3</v>
       </c>
       <c r="K731" t="n">
-        <v>12.06303711946447</v>
+        <v>12.06310897532417</v>
       </c>
     </row>
     <row r="732">
@@ -30453,7 +30453,7 @@
         <v>3</v>
       </c>
       <c r="K732" t="n">
-        <v>11.99444637636747</v>
+        <v>11.9961213858822</v>
       </c>
     </row>
     <row r="733">
@@ -30494,7 +30494,7 @@
         <v>3</v>
       </c>
       <c r="K733" t="n">
-        <v>11.99717312136171</v>
+        <v>11.98540031168541</v>
       </c>
     </row>
     <row r="734">
@@ -30535,7 +30535,7 @@
         <v>3</v>
       </c>
       <c r="K734" t="n">
-        <v>12.08575964011648</v>
+        <v>12.09651263244188</v>
       </c>
     </row>
     <row r="735">
@@ -30576,7 +30576,7 @@
         <v>3</v>
       </c>
       <c r="K735" t="n">
-        <v>12.05019264401203</v>
+        <v>12.08284121011117</v>
       </c>
     </row>
     <row r="736">
@@ -30617,7 +30617,7 @@
         <v>3</v>
       </c>
       <c r="K736" t="n">
-        <v>11.84456058307084</v>
+        <v>11.85368133955641</v>
       </c>
     </row>
     <row r="737">
@@ -30658,7 +30658,7 @@
         <v>3</v>
       </c>
       <c r="K737" t="n">
-        <v>11.39447657173803</v>
+        <v>11.37526068604558</v>
       </c>
     </row>
     <row r="738">
@@ -30699,7 +30699,7 @@
         <v>3</v>
       </c>
       <c r="K738" t="n">
-        <v>11.39447657173803</v>
+        <v>11.37526068604558</v>
       </c>
     </row>
     <row r="739">
@@ -30740,7 +30740,7 @@
         <v>3</v>
       </c>
       <c r="K739" t="n">
-        <v>11.23667906757831</v>
+        <v>11.22827577844529</v>
       </c>
     </row>
     <row r="740">
@@ -30781,7 +30781,7 @@
         <v>3</v>
       </c>
       <c r="K740" t="n">
-        <v>11.23667906757831</v>
+        <v>11.22827577844529</v>
       </c>
     </row>
     <row r="741">
@@ -30822,7 +30822,7 @@
         <v>3</v>
       </c>
       <c r="K741" t="n">
-        <v>11.15193366108053</v>
+        <v>11.13008198559545</v>
       </c>
     </row>
     <row r="742">
@@ -30863,7 +30863,7 @@
         <v>3</v>
       </c>
       <c r="K742" t="n">
-        <v>11.1571956204049</v>
+        <v>11.1690742727488</v>
       </c>
     </row>
     <row r="743">
@@ -30904,7 +30904,7 @@
         <v>3</v>
       </c>
       <c r="K743" t="n">
-        <v>11.31145186426089</v>
+        <v>11.3389182463484</v>
       </c>
     </row>
     <row r="744">
@@ -30945,7 +30945,7 @@
         <v>3</v>
       </c>
       <c r="K744" t="n">
-        <v>11.37728680904353</v>
+        <v>11.38646467874362</v>
       </c>
     </row>
     <row r="745">
@@ -30986,7 +30986,7 @@
         <v>3</v>
       </c>
       <c r="K745" t="n">
-        <v>11.80397094210926</v>
+        <v>11.82342431308706</v>
       </c>
     </row>
     <row r="746">
@@ -31027,7 +31027,7 @@
         <v>3</v>
       </c>
       <c r="K746" t="n">
-        <v>12.16726027947524</v>
+        <v>12.19377695822308</v>
       </c>
     </row>
     <row r="747">
@@ -31068,7 +31068,7 @@
         <v>3</v>
       </c>
       <c r="K747" t="n">
-        <v>12.16726027947524</v>
+        <v>12.19377695822308</v>
       </c>
     </row>
     <row r="748">
@@ -31109,7 +31109,7 @@
         <v>3</v>
       </c>
       <c r="K748" t="n">
-        <v>12.16726027947524</v>
+        <v>12.19377695822308</v>
       </c>
     </row>
     <row r="749">
@@ -31150,7 +31150,7 @@
         <v>3</v>
       </c>
       <c r="K749" t="n">
-        <v>12.30185739882523</v>
+        <v>12.33084068851601</v>
       </c>
     </row>
     <row r="750">
@@ -31191,7 +31191,7 @@
         <v>3</v>
       </c>
       <c r="K750" t="n">
-        <v>12.78309918300961</v>
+        <v>12.7822997463078</v>
       </c>
     </row>
     <row r="751">
@@ -31232,7 +31232,7 @@
         <v>3</v>
       </c>
       <c r="K751" t="n">
-        <v>12.78309918300961</v>
+        <v>12.7822997463078</v>
       </c>
     </row>
     <row r="752">
@@ -31273,7 +31273,7 @@
         <v>3</v>
       </c>
       <c r="K752" t="n">
-        <v>12.95048505861364</v>
+        <v>12.97740260138807</v>
       </c>
     </row>
     <row r="753">
@@ -31314,7 +31314,7 @@
         <v>3</v>
       </c>
       <c r="K753" t="n">
-        <v>13.34478734312878</v>
+        <v>13.35275544310975</v>
       </c>
     </row>
     <row r="754">
@@ -31355,7 +31355,7 @@
         <v>3</v>
       </c>
       <c r="K754" t="n">
-        <v>13.37074339622259</v>
+        <v>13.35975122638266</v>
       </c>
     </row>
     <row r="755">
@@ -31396,7 +31396,7 @@
         <v>3</v>
       </c>
       <c r="K755" t="n">
-        <v>13.36792746283763</v>
+        <v>13.3693112460323</v>
       </c>
     </row>
     <row r="756">
@@ -31437,7 +31437,7 @@
         <v>3</v>
       </c>
       <c r="K756" t="n">
-        <v>13.35437604347166</v>
+        <v>13.34125040974723</v>
       </c>
     </row>
     <row r="757">
@@ -31478,7 +31478,7 @@
         <v>3</v>
       </c>
       <c r="K757" t="n">
-        <v>13.09693231667243</v>
+        <v>13.10163575306451</v>
       </c>
     </row>
     <row r="758">
@@ -31519,7 +31519,7 @@
         <v>3</v>
       </c>
       <c r="K758" t="n">
-        <v>12.91736847823623</v>
+        <v>12.94446589434488</v>
       </c>
     </row>
     <row r="759">
@@ -31560,7 +31560,7 @@
         <v>3</v>
       </c>
       <c r="K759" t="n">
-        <v>12.76765057204529</v>
+        <v>12.73937802434984</v>
       </c>
     </row>
     <row r="760">
@@ -31601,7 +31601,7 @@
         <v>3</v>
       </c>
       <c r="K760" t="n">
-        <v>12.69353243342853</v>
+        <v>12.69875192168545</v>
       </c>
     </row>
     <row r="761">
@@ -31642,7 +31642,7 @@
         <v>3</v>
       </c>
       <c r="K761" t="n">
-        <v>12.58895012359282</v>
+        <v>12.58901627016309</v>
       </c>
     </row>
     <row r="762">
@@ -31683,7 +31683,7 @@
         <v>3</v>
       </c>
       <c r="K762" t="n">
-        <v>12.42470672592619</v>
+        <v>12.43162075048071</v>
       </c>
     </row>
     <row r="763">
@@ -31724,7 +31724,7 @@
         <v>3</v>
       </c>
       <c r="K763" t="n">
-        <v>12.26680028901702</v>
+        <v>12.27379181923583</v>
       </c>
     </row>
     <row r="764">
@@ -31765,7 +31765,7 @@
         <v>3</v>
       </c>
       <c r="K764" t="n">
-        <v>11.89190788496205</v>
+        <v>11.95802568283935</v>
       </c>
     </row>
     <row r="765">
@@ -31806,7 +31806,7 @@
         <v>3</v>
       </c>
       <c r="K765" t="n">
-        <v>11.89190788496205</v>
+        <v>11.84888626362425</v>
       </c>
     </row>
     <row r="766">
@@ -31847,7 +31847,7 @@
         <v>3</v>
       </c>
       <c r="K766" t="n">
-        <v>11.67704269902975</v>
+        <v>11.66568469607117</v>
       </c>
     </row>
     <row r="767">
@@ -31888,7 +31888,7 @@
         <v>3</v>
       </c>
       <c r="K767" t="n">
-        <v>11.64415488947232</v>
+        <v>11.65298385187852</v>
       </c>
     </row>
     <row r="768">
@@ -31929,7 +31929,7 @@
         <v>3</v>
       </c>
       <c r="K768" t="n">
-        <v>11.64033421254849</v>
+        <v>11.65380875206768</v>
       </c>
     </row>
     <row r="769">
@@ -31970,7 +31970,7 @@
         <v>3</v>
       </c>
       <c r="K769" t="n">
-        <v>11.85096145997042</v>
+        <v>11.85083220385463</v>
       </c>
     </row>
     <row r="770">
@@ -32011,7 +32011,7 @@
         <v>3</v>
       </c>
       <c r="K770" t="n">
-        <v>12.04094588660456</v>
+        <v>12.02117328429266</v>
       </c>
     </row>
     <row r="771">
@@ -32052,7 +32052,7 @@
         <v>3</v>
       </c>
       <c r="K771" t="n">
-        <v>12.14224169435719</v>
+        <v>12.1373339551059</v>
       </c>
     </row>
     <row r="772">
@@ -32093,7 +32093,7 @@
         <v>3</v>
       </c>
       <c r="K772" t="n">
-        <v>12.17880814252204</v>
+        <v>12.20640734971584</v>
       </c>
     </row>
     <row r="773">
@@ -32134,7 +32134,7 @@
         <v>3</v>
       </c>
       <c r="K773" t="n">
-        <v>12.27644773240924</v>
+        <v>12.26936210139702</v>
       </c>
     </row>
     <row r="774">
@@ -32175,7 +32175,7 @@
         <v>3</v>
       </c>
       <c r="K774" t="n">
-        <v>12.27644773240924</v>
+        <v>12.26936210139702</v>
       </c>
     </row>
     <row r="775">
@@ -32216,7 +32216,7 @@
         <v>3</v>
       </c>
       <c r="K775" t="n">
-        <v>12.23218171156939</v>
+        <v>12.24302674050115</v>
       </c>
     </row>
     <row r="776">
@@ -32257,7 +32257,7 @@
         <v>3</v>
       </c>
       <c r="K776" t="n">
-        <v>12.24208486651622</v>
+        <v>12.24187620049771</v>
       </c>
     </row>
     <row r="777">
@@ -32298,7 +32298,7 @@
         <v>3</v>
       </c>
       <c r="K777" t="n">
-        <v>12.24208486651622</v>
+        <v>12.24187620049771</v>
       </c>
     </row>
     <row r="778">
@@ -32339,7 +32339,7 @@
         <v>3</v>
       </c>
       <c r="K778" t="n">
-        <v>12.24208486651622</v>
+        <v>12.24187620049771</v>
       </c>
     </row>
     <row r="779">
@@ -32380,7 +32380,7 @@
         <v>3</v>
       </c>
       <c r="K779" t="n">
-        <v>12.241789653229</v>
+        <v>12.12800502217932</v>
       </c>
     </row>
     <row r="780">
@@ -32421,7 +32421,7 @@
         <v>3</v>
       </c>
       <c r="K780" t="n">
-        <v>12.15668120916344</v>
+        <v>12.16066227138671</v>
       </c>
     </row>
     <row r="781">
@@ -32462,7 +32462,7 @@
         <v>3</v>
       </c>
       <c r="K781" t="n">
-        <v>12.0796094977298</v>
+        <v>12.0799154126204</v>
       </c>
     </row>
     <row r="782">
@@ -32503,7 +32503,7 @@
         <v>3</v>
       </c>
       <c r="K782" t="n">
-        <v>11.74143510311952</v>
+        <v>11.74178971400586</v>
       </c>
     </row>
     <row r="783">
@@ -32544,7 +32544,7 @@
         <v>3</v>
       </c>
       <c r="K783" t="n">
-        <v>11.58598802590353</v>
+        <v>11.59293827825005</v>
       </c>
     </row>
     <row r="784">
@@ -32585,7 +32585,7 @@
         <v>3</v>
       </c>
       <c r="K784" t="n">
-        <v>11.46268003286958</v>
+        <v>11.46841636767131</v>
       </c>
     </row>
     <row r="785">
@@ -32626,7 +32626,7 @@
         <v>3</v>
       </c>
       <c r="K785" t="n">
-        <v>10.90877953588958</v>
+        <v>10.9091611464852</v>
       </c>
     </row>
     <row r="786">
@@ -32667,7 +32667,7 @@
         <v>3</v>
       </c>
       <c r="K786" t="n">
-        <v>10.90877953588958</v>
+        <v>10.9091611464852</v>
       </c>
     </row>
     <row r="787">
@@ -32708,7 +32708,7 @@
         <v>3</v>
       </c>
       <c r="K787" t="n">
-        <v>10.90877953588958</v>
+        <v>10.9091611464852</v>
       </c>
     </row>
     <row r="788">
@@ -32749,7 +32749,7 @@
         <v>3</v>
       </c>
       <c r="K788" t="n">
-        <v>10.89804667605525</v>
+        <v>10.90173048919135</v>
       </c>
     </row>
     <row r="789">
@@ -32790,7 +32790,7 @@
         <v>3</v>
       </c>
       <c r="K789" t="n">
-        <v>10.6372412839552</v>
+        <v>10.63715668704324</v>
       </c>
     </row>
     <row r="790">
@@ -32831,7 +32831,7 @@
         <v>3</v>
       </c>
       <c r="K790" t="n">
-        <v>10.6372412839552</v>
+        <v>10.63715668704324</v>
       </c>
     </row>
     <row r="791">
@@ -32872,7 +32872,7 @@
         <v>3</v>
       </c>
       <c r="K791" t="n">
-        <v>10.6372412839552</v>
+        <v>10.63715668704324</v>
       </c>
     </row>
     <row r="792">
@@ -32913,7 +32913,7 @@
         <v>3</v>
       </c>
       <c r="K792" t="n">
-        <v>11.11248164712619</v>
+        <v>11.111777718237</v>
       </c>
     </row>
     <row r="793">
@@ -32954,7 +32954,7 @@
         <v>3</v>
       </c>
       <c r="K793" t="n">
-        <v>11.1303269369723</v>
+        <v>11.12393318166838</v>
       </c>
     </row>
     <row r="794">
@@ -32995,7 +32995,7 @@
         <v>3</v>
       </c>
       <c r="K794" t="n">
-        <v>11.2496812739395</v>
+        <v>11.24454849391147</v>
       </c>
     </row>
     <row r="795">
@@ -33036,7 +33036,7 @@
         <v>3</v>
       </c>
       <c r="K795" t="n">
-        <v>11.2496812739395</v>
+        <v>11.24454849391147</v>
       </c>
     </row>
     <row r="796">
@@ -33077,7 +33077,7 @@
         <v>3</v>
       </c>
       <c r="K796" t="n">
-        <v>11.2496812739395</v>
+        <v>11.24454849391147</v>
       </c>
     </row>
     <row r="797">
@@ -33118,7 +33118,7 @@
         <v>3</v>
       </c>
       <c r="K797" t="n">
-        <v>11.27027512297909</v>
+        <v>11.27071320794287</v>
       </c>
     </row>
     <row r="798">
@@ -33159,7 +33159,7 @@
         <v>3</v>
       </c>
       <c r="K798" t="n">
-        <v>10.9812380606337</v>
+        <v>10.9852286005524</v>
       </c>
     </row>
     <row r="799">
@@ -33200,7 +33200,7 @@
         <v>15</v>
       </c>
       <c r="K799" t="n">
-        <v>11.47715233624656</v>
+        <v>11.47538915658819</v>
       </c>
     </row>
     <row r="800">
@@ -33241,7 +33241,7 @@
         <v>15</v>
       </c>
       <c r="K800" t="n">
-        <v>14.86908571659085</v>
+        <v>14.85882467835489</v>
       </c>
     </row>
     <row r="801">
@@ -33282,7 +33282,7 @@
         <v>15</v>
       </c>
       <c r="K801" t="n">
-        <v>16.29521350041209</v>
+        <v>16.28443042181838</v>
       </c>
     </row>
     <row r="802">
@@ -33323,7 +33323,7 @@
         <v>15</v>
       </c>
       <c r="K802" t="n">
-        <v>21.73230353325222</v>
+        <v>21.73270856745602</v>
       </c>
     </row>
     <row r="803">
@@ -33364,7 +33364,7 @@
         <v>15</v>
       </c>
       <c r="K803" t="n">
-        <v>21.73230353325222</v>
+        <v>21.73270856745602</v>
       </c>
     </row>
     <row r="804">
@@ -33405,7 +33405,7 @@
         <v>15</v>
       </c>
       <c r="K804" t="n">
-        <v>8.118514307678311</v>
+        <v>8.119903727494155</v>
       </c>
     </row>
     <row r="805">
@@ -33446,7 +33446,7 @@
         <v>15</v>
       </c>
       <c r="K805" t="n">
-        <v>8.096183421429028</v>
+        <v>8.104068775254905</v>
       </c>
     </row>
     <row r="806">
@@ -33487,7 +33487,7 @@
         <v>15</v>
       </c>
       <c r="K806" t="n">
-        <v>7.83125238581976</v>
+        <v>7.834576293056161</v>
       </c>
     </row>
     <row r="807">
@@ -33528,7 +33528,7 @@
         <v>15</v>
       </c>
       <c r="K807" t="n">
-        <v>7.712398785570351</v>
+        <v>7.713141469417097</v>
       </c>
     </row>
     <row r="808">
@@ -33569,7 +33569,7 @@
         <v>15</v>
       </c>
       <c r="K808" t="n">
-        <v>7.713664677151737</v>
+        <v>7.713427859944241</v>
       </c>
     </row>
     <row r="809">
@@ -33610,7 +33610,7 @@
         <v>15</v>
       </c>
       <c r="K809" t="n">
-        <v>7.713664677151737</v>
+        <v>7.713427859944241</v>
       </c>
     </row>
     <row r="810">
@@ -33651,7 +33651,7 @@
         <v>15</v>
       </c>
       <c r="K810" t="n">
-        <v>7.667933508527102</v>
+        <v>7.669311507056754</v>
       </c>
     </row>
     <row r="811">
@@ -33692,7 +33692,7 @@
         <v>15</v>
       </c>
       <c r="K811" t="n">
-        <v>7.548734718618934</v>
+        <v>7.551143762363481</v>
       </c>
     </row>
     <row r="812">
@@ -33733,7 +33733,7 @@
         <v>15</v>
       </c>
       <c r="K812" t="n">
-        <v>7.548734718618934</v>
+        <v>7.551143762363481</v>
       </c>
     </row>
     <row r="813">
@@ -33774,7 +33774,7 @@
         <v>15</v>
       </c>
       <c r="K813" t="n">
-        <v>7.396912646606284</v>
+        <v>7.403049138217716</v>
       </c>
     </row>
     <row r="814">
@@ -33815,7 +33815,7 @@
         <v>15</v>
       </c>
       <c r="K814" t="n">
-        <v>7.396912646606284</v>
+        <v>7.403049138217716</v>
       </c>
     </row>
     <row r="815">
@@ -33856,7 +33856,7 @@
         <v>15</v>
       </c>
       <c r="K815" t="n">
-        <v>7.320252971938328</v>
+        <v>7.32298606994592</v>
       </c>
     </row>
     <row r="816">
@@ -33897,7 +33897,7 @@
         <v>15</v>
       </c>
       <c r="K816" t="n">
-        <v>7.239857077667367</v>
+        <v>7.240606853843936</v>
       </c>
     </row>
     <row r="817">
@@ -33938,7 +33938,7 @@
         <v>15</v>
       </c>
       <c r="K817" t="n">
-        <v>7.199295819105686</v>
+        <v>7.199909895637294</v>
       </c>
     </row>
     <row r="818">
@@ -33979,7 +33979,7 @@
         <v>15</v>
       </c>
       <c r="K818" t="n">
-        <v>7.256348266322199</v>
+        <v>7.253041107143696</v>
       </c>
     </row>
     <row r="819">
@@ -34020,7 +34020,7 @@
         <v>15</v>
       </c>
       <c r="K819" t="n">
-        <v>7.714576174838844</v>
+        <v>7.713408152961761</v>
       </c>
     </row>
     <row r="820">
@@ -34061,7 +34061,7 @@
         <v>15</v>
       </c>
       <c r="K820" t="n">
-        <v>7.806655421192318</v>
+        <v>7.805754974922663</v>
       </c>
     </row>
     <row r="821">
@@ -34102,7 +34102,7 @@
         <v>15</v>
       </c>
       <c r="K821" t="n">
-        <v>7.968306873932931</v>
+        <v>7.964268095842725</v>
       </c>
     </row>
     <row r="822">
@@ -34143,7 +34143,7 @@
         <v>15</v>
       </c>
       <c r="K822" t="n">
-        <v>8.108509975853293</v>
+        <v>8.108056073309475</v>
       </c>
     </row>
     <row r="823">
@@ -34184,7 +34184,7 @@
         <v>15</v>
       </c>
       <c r="K823" t="n">
-        <v>8.127305900666336</v>
+        <v>8.127345282007774</v>
       </c>
     </row>
     <row r="824">
@@ -34225,7 +34225,7 @@
         <v>15</v>
       </c>
       <c r="K824" t="n">
-        <v>8.108983998509961</v>
+        <v>8.10937840376187</v>
       </c>
     </row>
     <row r="825">
@@ -34266,7 +34266,7 @@
         <v>15</v>
       </c>
       <c r="K825" t="n">
-        <v>8.104036600918691</v>
+        <v>8.106125210304572</v>
       </c>
     </row>
     <row r="826">
@@ -34307,7 +34307,7 @@
         <v>15</v>
       </c>
       <c r="K826" t="n">
-        <v>8.012610878891133</v>
+        <v>8.012986959812888</v>
       </c>
     </row>
     <row r="827">
@@ -34348,7 +34348,7 @@
         <v>15</v>
       </c>
       <c r="K827" t="n">
-        <v>8.009635896575176</v>
+        <v>8.010728641557851</v>
       </c>
     </row>
     <row r="828">
@@ -34389,7 +34389,7 @@
         <v>15</v>
       </c>
       <c r="K828" t="n">
-        <v>8.006697691057722</v>
+        <v>8.005974464752878</v>
       </c>
     </row>
     <row r="829">
@@ -34430,7 +34430,7 @@
         <v>15</v>
       </c>
       <c r="K829" t="n">
-        <v>8.006697691057722</v>
+        <v>8.005974464752878</v>
       </c>
     </row>
     <row r="830">
@@ -34471,7 +34471,7 @@
         <v>15</v>
       </c>
       <c r="K830" t="n">
-        <v>8.006697691057722</v>
+        <v>8.005974464752878</v>
       </c>
     </row>
     <row r="831">
@@ -34512,7 +34512,7 @@
         <v>15</v>
       </c>
       <c r="K831" t="n">
-        <v>7.990069215900757</v>
+        <v>7.990250576574452</v>
       </c>
     </row>
     <row r="832">
@@ -34553,7 +34553,7 @@
         <v>15</v>
       </c>
       <c r="K832" t="n">
-        <v>7.972786345727271</v>
+        <v>7.95591894222438</v>
       </c>
     </row>
     <row r="833">
@@ -34594,7 +34594,7 @@
         <v>15</v>
       </c>
       <c r="K833" t="n">
-        <v>7.952307603976189</v>
+        <v>7.953692980937775</v>
       </c>
     </row>
     <row r="834">
@@ -34635,7 +34635,7 @@
         <v>15</v>
       </c>
       <c r="K834" t="n">
-        <v>7.93225907871838</v>
+        <v>7.932588388417184</v>
       </c>
     </row>
     <row r="835">
@@ -34676,7 +34676,7 @@
         <v>15</v>
       </c>
       <c r="K835" t="n">
-        <v>7.879500774659473</v>
+        <v>7.879473517638802</v>
       </c>
     </row>
     <row r="836">
@@ -34717,7 +34717,7 @@
         <v>15</v>
       </c>
       <c r="K836" t="n">
-        <v>7.879627153900471</v>
+        <v>7.879541018398344</v>
       </c>
     </row>
     <row r="837">
@@ -34758,7 +34758,7 @@
         <v>15</v>
       </c>
       <c r="K837" t="n">
-        <v>7.882608349234774</v>
+        <v>7.882530045859445</v>
       </c>
     </row>
     <row r="838">
@@ -34799,7 +34799,7 @@
         <v>15</v>
       </c>
       <c r="K838" t="n">
-        <v>7.879672402084864</v>
+        <v>7.880270677339019</v>
       </c>
     </row>
     <row r="839">
@@ -34840,7 +34840,7 @@
         <v>15</v>
       </c>
       <c r="K839" t="n">
-        <v>8.025670711125565</v>
+        <v>8.032733819654311</v>
       </c>
     </row>
     <row r="840">
@@ -34881,7 +34881,7 @@
         <v>15</v>
       </c>
       <c r="K840" t="n">
-        <v>8.199261728623892</v>
+        <v>8.206837245264143</v>
       </c>
     </row>
     <row r="841">
@@ -34922,7 +34922,7 @@
         <v>15</v>
       </c>
       <c r="K841" t="n">
-        <v>8.465261169348235</v>
+        <v>8.463684075990503</v>
       </c>
     </row>
     <row r="842">
@@ -34963,7 +34963,7 @@
         <v>15</v>
       </c>
       <c r="K842" t="n">
-        <v>8.570407141956462</v>
+        <v>8.565529843566759</v>
       </c>
     </row>
     <row r="843">
@@ -35004,7 +35004,7 @@
         <v>15</v>
       </c>
       <c r="K843" t="n">
-        <v>8.684496142895249</v>
+        <v>8.683768185220636</v>
       </c>
     </row>
     <row r="844">
@@ -35045,7 +35045,7 @@
         <v>15</v>
       </c>
       <c r="K844" t="n">
-        <v>8.699701555632165</v>
+        <v>8.699513942316511</v>
       </c>
     </row>
     <row r="845">
@@ -35086,7 +35086,7 @@
         <v>15</v>
       </c>
       <c r="K845" t="n">
-        <v>8.696194770380107</v>
+        <v>8.696993571304105</v>
       </c>
     </row>
     <row r="846">
@@ -35127,7 +35127,7 @@
         <v>15</v>
       </c>
       <c r="K846" t="n">
-        <v>8.677503576964556</v>
+        <v>8.679991846676121</v>
       </c>
     </row>
     <row r="847">
@@ -35168,7 +35168,7 @@
         <v>15</v>
       </c>
       <c r="K847" t="n">
-        <v>8.677503576964556</v>
+        <v>8.679991846676121</v>
       </c>
     </row>
     <row r="848">
@@ -35209,7 +35209,7 @@
         <v>15</v>
       </c>
       <c r="K848" t="n">
-        <v>8.448089922706933</v>
+        <v>8.452826304108875</v>
       </c>
     </row>
     <row r="849">
@@ -35250,7 +35250,7 @@
         <v>15</v>
       </c>
       <c r="K849" t="n">
-        <v>8.448089922706933</v>
+        <v>8.452826304108875</v>
       </c>
     </row>
     <row r="850">
@@ -35291,7 +35291,7 @@
         <v>15</v>
       </c>
       <c r="K850" t="n">
-        <v>8.336822060506137</v>
+        <v>8.338594749377791</v>
       </c>
     </row>
     <row r="851">
@@ -35332,7 +35332,7 @@
         <v>15</v>
       </c>
       <c r="K851" t="n">
-        <v>8.336822060506137</v>
+        <v>8.338594749377791</v>
       </c>
     </row>
     <row r="852">
@@ -35373,7 +35373,7 @@
         <v>15</v>
       </c>
       <c r="K852" t="n">
-        <v>8.336822060506137</v>
+        <v>8.338594749377791</v>
       </c>
     </row>
     <row r="853">
@@ -35414,7 +35414,7 @@
         <v>15</v>
       </c>
       <c r="K853" t="n">
-        <v>8.147518697921111</v>
+        <v>8.149421010913416</v>
       </c>
     </row>
     <row r="854">
@@ -35455,7 +35455,7 @@
         <v>15</v>
       </c>
       <c r="K854" t="n">
-        <v>8.063642391381936</v>
+        <v>8.067956697897623</v>
       </c>
     </row>
     <row r="855">
@@ -35496,7 +35496,7 @@
         <v>15</v>
       </c>
       <c r="K855" t="n">
-        <v>7.99126331278467</v>
+        <v>7.991689966689593</v>
       </c>
     </row>
     <row r="856">
@@ -35537,7 +35537,7 @@
         <v>15</v>
       </c>
       <c r="K856" t="n">
-        <v>7.913405313829859</v>
+        <v>7.916695593805382</v>
       </c>
     </row>
     <row r="857">
@@ -35578,7 +35578,7 @@
         <v>15</v>
       </c>
       <c r="K857" t="n">
-        <v>7.821729876522761</v>
+        <v>7.821420584254957</v>
       </c>
     </row>
     <row r="858">
@@ -35619,7 +35619,7 @@
         <v>15</v>
       </c>
       <c r="K858" t="n">
-        <v>7.869047233398522</v>
+        <v>7.868853334806307</v>
       </c>
     </row>
     <row r="859">
@@ -35660,7 +35660,7 @@
         <v>15</v>
       </c>
       <c r="K859" t="n">
-        <v>7.870974637775676</v>
+        <v>7.870152942206765</v>
       </c>
     </row>
     <row r="860">
@@ -35701,7 +35701,7 @@
         <v>15</v>
       </c>
       <c r="K860" t="n">
-        <v>7.891566055398275</v>
+        <v>7.903919708613004</v>
       </c>
     </row>
     <row r="861">
@@ -35742,7 +35742,7 @@
         <v>15</v>
       </c>
       <c r="K861" t="n">
-        <v>7.90543082412908</v>
+        <v>7.904904802098965</v>
       </c>
     </row>
     <row r="862">
@@ -35783,7 +35783,7 @@
         <v>15</v>
       </c>
       <c r="K862" t="n">
-        <v>7.905699559640038</v>
+        <v>7.906047246735858</v>
       </c>
     </row>
     <row r="863">
@@ -35824,7 +35824,7 @@
         <v>15</v>
       </c>
       <c r="K863" t="n">
-        <v>7.905699559640038</v>
+        <v>7.906047246735858</v>
       </c>
     </row>
     <row r="864">
@@ -35865,7 +35865,7 @@
         <v>15</v>
       </c>
       <c r="K864" t="n">
-        <v>7.995510975294768</v>
+        <v>7.998606463657565</v>
       </c>
     </row>
     <row r="865">
@@ -35906,7 +35906,7 @@
         <v>15</v>
       </c>
       <c r="K865" t="n">
-        <v>8.016027347996358</v>
+        <v>8.017664346847644</v>
       </c>
     </row>
     <row r="866">
@@ -35947,7 +35947,7 @@
         <v>15</v>
       </c>
       <c r="K866" t="n">
-        <v>7.983043959946182</v>
+        <v>7.983790706657906</v>
       </c>
     </row>
     <row r="867">
@@ -35988,7 +35988,7 @@
         <v>15</v>
       </c>
       <c r="K867" t="n">
-        <v>7.929058492439354</v>
+        <v>7.932726441155485</v>
       </c>
     </row>
     <row r="868">
@@ -36029,7 +36029,7 @@
         <v>15</v>
       </c>
       <c r="K868" t="n">
-        <v>7.897348099340872</v>
+        <v>7.897807510195624</v>
       </c>
     </row>
     <row r="869">
@@ -36070,7 +36070,7 @@
         <v>15</v>
       </c>
       <c r="K869" t="n">
-        <v>7.864824530627885</v>
+        <v>7.864315868209005</v>
       </c>
     </row>
     <row r="870">
@@ -36111,7 +36111,7 @@
         <v>15</v>
       </c>
       <c r="K870" t="n">
-        <v>7.890239499082802</v>
+        <v>7.889726034319747</v>
       </c>
     </row>
     <row r="871">
@@ -36152,7 +36152,7 @@
         <v>15</v>
       </c>
       <c r="K871" t="n">
-        <v>7.964058370997098</v>
+        <v>7.962966582882214</v>
       </c>
     </row>
     <row r="872">
@@ -36193,7 +36193,7 @@
         <v>15</v>
       </c>
       <c r="K872" t="n">
-        <v>8.017375773941534</v>
+        <v>8.016533974847052</v>
       </c>
     </row>
     <row r="873">
@@ -36234,7 +36234,7 @@
         <v>15</v>
       </c>
       <c r="K873" t="n">
-        <v>8.024527424938098</v>
+        <v>8.02130451378029</v>
       </c>
     </row>
     <row r="874">
@@ -36275,7 +36275,7 @@
         <v>15</v>
       </c>
       <c r="K874" t="n">
-        <v>8.085304775903023</v>
+        <v>8.084622742969383</v>
       </c>
     </row>
     <row r="875">
@@ -36316,7 +36316,7 @@
         <v>15</v>
       </c>
       <c r="K875" t="n">
-        <v>8.096044285790475</v>
+        <v>8.094966846613239</v>
       </c>
     </row>
     <row r="876">
@@ -36357,7 +36357,7 @@
         <v>15</v>
       </c>
       <c r="K876" t="n">
-        <v>8.096044285790475</v>
+        <v>8.094966846613239</v>
       </c>
     </row>
     <row r="877">
@@ -36398,7 +36398,7 @@
         <v>15</v>
       </c>
       <c r="K877" t="n">
-        <v>8.110533408638272</v>
+        <v>8.110166420427403</v>
       </c>
     </row>
     <row r="878">
@@ -36439,7 +36439,7 @@
         <v>15</v>
       </c>
       <c r="K878" t="n">
-        <v>8.113787015443322</v>
+        <v>8.112385584208136</v>
       </c>
     </row>
     <row r="879">
@@ -36480,7 +36480,7 @@
         <v>15</v>
       </c>
       <c r="K879" t="n">
-        <v>8.129754919726599</v>
+        <v>8.12944880205656</v>
       </c>
     </row>
     <row r="880">
@@ -36521,7 +36521,7 @@
         <v>15</v>
       </c>
       <c r="K880" t="n">
-        <v>8.132339611824881</v>
+        <v>8.131271759640452</v>
       </c>
     </row>
     <row r="881">
@@ -36562,7 +36562,7 @@
         <v>15</v>
       </c>
       <c r="K881" t="n">
-        <v>8.153616291429023</v>
+        <v>8.153518357417308</v>
       </c>
     </row>
     <row r="882">
@@ -36603,7 +36603,7 @@
         <v>15</v>
       </c>
       <c r="K882" t="n">
-        <v>8.155189628629758</v>
+        <v>8.154481842521511</v>
       </c>
     </row>
     <row r="883">
@@ -36644,7 +36644,7 @@
         <v>15</v>
       </c>
       <c r="K883" t="n">
-        <v>8.18525616598332</v>
+        <v>8.18513343413235</v>
       </c>
     </row>
     <row r="884">
@@ -36685,7 +36685,7 @@
         <v>15</v>
       </c>
       <c r="K884" t="n">
-        <v>8.184740236418625</v>
+        <v>8.18492560297684</v>
       </c>
     </row>
     <row r="885">
@@ -36726,7 +36726,7 @@
         <v>15</v>
       </c>
       <c r="K885" t="n">
-        <v>8.172388564125416</v>
+        <v>8.171427785419828</v>
       </c>
     </row>
     <row r="886">
@@ -36767,7 +36767,7 @@
         <v>15</v>
       </c>
       <c r="K886" t="n">
-        <v>8.189107986717081</v>
+        <v>8.188578129246416</v>
       </c>
     </row>
     <row r="887">
@@ -36808,7 +36808,7 @@
         <v>15</v>
       </c>
       <c r="K887" t="n">
-        <v>8.220160025137268</v>
+        <v>8.217759789020585</v>
       </c>
     </row>
     <row r="888">
@@ -36849,7 +36849,7 @@
         <v>15</v>
       </c>
       <c r="K888" t="n">
-        <v>8.240644664662339</v>
+        <v>8.240289557396054</v>
       </c>
     </row>
     <row r="889">
@@ -36890,7 +36890,7 @@
         <v>15</v>
       </c>
       <c r="K889" t="n">
-        <v>8.307114933192983</v>
+        <v>8.30436654246869</v>
       </c>
     </row>
     <row r="890">
@@ -36931,7 +36931,7 @@
         <v>15</v>
       </c>
       <c r="K890" t="n">
-        <v>8.331287594132842</v>
+        <v>8.330263603328007</v>
       </c>
     </row>
     <row r="891">
@@ -36972,7 +36972,7 @@
         <v>15</v>
       </c>
       <c r="K891" t="n">
-        <v>8.196790183492965</v>
+        <v>8.195848371486919</v>
       </c>
     </row>
     <row r="892">
@@ -37013,7 +37013,7 @@
         <v>15</v>
       </c>
       <c r="K892" t="n">
-        <v>8.196790183492965</v>
+        <v>8.195848371486919</v>
       </c>
     </row>
     <row r="893">
@@ -37054,7 +37054,7 @@
         <v>15</v>
       </c>
       <c r="K893" t="n">
-        <v>7.722711314280213</v>
+        <v>7.727218062910691</v>
       </c>
     </row>
     <row r="894">
@@ -37095,7 +37095,7 @@
         <v>15</v>
       </c>
       <c r="K894" t="n">
-        <v>7.678078644550113</v>
+        <v>7.450422762134465</v>
       </c>
     </row>
     <row r="895">
@@ -37136,7 +37136,7 @@
         <v>15</v>
       </c>
       <c r="K895" t="n">
-        <v>7.443993939752657</v>
+        <v>7.450422762134465</v>
       </c>
     </row>
     <row r="896">
@@ -37177,7 +37177,7 @@
         <v>15</v>
       </c>
       <c r="K896" t="n">
-        <v>7.211907259744146</v>
+        <v>7.221410992403285</v>
       </c>
     </row>
     <row r="897">
@@ -37218,7 +37218,7 @@
         <v>15</v>
       </c>
       <c r="K897" t="n">
-        <v>7.211907259744146</v>
+        <v>7.221410992403285</v>
       </c>
     </row>
     <row r="898">
@@ -37259,7 +37259,7 @@
         <v>15</v>
       </c>
       <c r="K898" t="n">
-        <v>6.990216985875503</v>
+        <v>6.996061590270203</v>
       </c>
     </row>
     <row r="899">
@@ -37300,7 +37300,7 @@
         <v>15</v>
       </c>
       <c r="K899" t="n">
-        <v>6.831282039974321</v>
+        <v>6.832978915620941</v>
       </c>
     </row>
     <row r="900">
@@ -37341,7 +37341,7 @@
         <v>15</v>
       </c>
       <c r="K900" t="n">
-        <v>6.656545662009725</v>
+        <v>6.66034970544243</v>
       </c>
     </row>
     <row r="901">
@@ -37382,7 +37382,7 @@
         <v>15</v>
       </c>
       <c r="K901" t="n">
-        <v>6.624720817679719</v>
+        <v>6.62411408327838</v>
       </c>
     </row>
     <row r="902">
@@ -37423,7 +37423,7 @@
         <v>15</v>
       </c>
       <c r="K902" t="n">
-        <v>6.658938938701485</v>
+        <v>6.656605657381196</v>
       </c>
     </row>
     <row r="903">
@@ -37464,7 +37464,7 @@
         <v>15</v>
       </c>
       <c r="K903" t="n">
-        <v>6.658938938701485</v>
+        <v>6.656605657381196</v>
       </c>
     </row>
     <row r="904">
@@ -37505,7 +37505,7 @@
         <v>15</v>
       </c>
       <c r="K904" t="n">
-        <v>6.713863596025063</v>
+        <v>6.70797136117511</v>
       </c>
     </row>
     <row r="905">
@@ -37546,7 +37546,7 @@
         <v>15</v>
       </c>
       <c r="K905" t="n">
-        <v>6.734214710585704</v>
+        <v>6.736069063457913</v>
       </c>
     </row>
     <row r="906">
@@ -37587,7 +37587,7 @@
         <v>15</v>
       </c>
       <c r="K906" t="n">
-        <v>6.728238191478929</v>
+        <v>6.732644290606647</v>
       </c>
     </row>
     <row r="907">
@@ -37628,7 +37628,7 @@
         <v>15</v>
       </c>
       <c r="K907" t="n">
-        <v>6.574203508919766</v>
+        <v>6.586161623649892</v>
       </c>
     </row>
     <row r="908">
@@ -37669,7 +37669,7 @@
         <v>15</v>
       </c>
       <c r="K908" t="n">
-        <v>6.484529236556608</v>
+        <v>6.487042053063791</v>
       </c>
     </row>
     <row r="909">
@@ -37710,7 +37710,7 @@
         <v>15</v>
       </c>
       <c r="K909" t="n">
-        <v>6.484529236556608</v>
+        <v>6.487042053063791</v>
       </c>
     </row>
     <row r="910">
@@ -37751,7 +37751,7 @@
         <v>15</v>
       </c>
       <c r="K910" t="n">
-        <v>6.378522603272511</v>
+        <v>6.377016991571851</v>
       </c>
     </row>
     <row r="911">
@@ -37792,7 +37792,7 @@
         <v>15</v>
       </c>
       <c r="K911" t="n">
-        <v>6.279311788894738</v>
+        <v>6.269973427843023</v>
       </c>
     </row>
     <row r="912">
@@ -37833,7 +37833,7 @@
         <v>15</v>
       </c>
       <c r="K912" t="n">
-        <v>5.998141336302388</v>
+        <v>6.003187710333971</v>
       </c>
     </row>
     <row r="913">
@@ -37874,7 +37874,7 @@
         <v>15</v>
       </c>
       <c r="K913" t="n">
-        <v>5.801928373026186</v>
+        <v>5.807030535797594</v>
       </c>
     </row>
     <row r="914">
@@ -37915,7 +37915,7 @@
         <v>15</v>
       </c>
       <c r="K914" t="n">
-        <v>5.64595186225668</v>
+        <v>5.651486942714144</v>
       </c>
     </row>
     <row r="915">
@@ -37956,7 +37956,7 @@
         <v>15</v>
       </c>
       <c r="K915" t="n">
-        <v>5.64595186225668</v>
+        <v>5.651486942714144</v>
       </c>
     </row>
     <row r="916">
@@ -37997,7 +37997,7 @@
         <v>15</v>
       </c>
       <c r="K916" t="n">
-        <v>5.457640218574324</v>
+        <v>5.456449133266219</v>
       </c>
     </row>
     <row r="917">
@@ -38038,7 +38038,7 @@
         <v>15</v>
       </c>
       <c r="K917" t="n">
-        <v>5.317011426297118</v>
+        <v>5.306659708990031</v>
       </c>
     </row>
     <row r="918">
@@ -38079,7 +38079,7 @@
         <v>15</v>
       </c>
       <c r="K918" t="n">
-        <v>5.295436244667705</v>
+        <v>5.287831319024627</v>
       </c>
     </row>
     <row r="919">
@@ -38120,7 +38120,7 @@
         <v>15</v>
       </c>
       <c r="K919" t="n">
-        <v>5.257712056259166</v>
+        <v>5.250630632893348</v>
       </c>
     </row>
     <row r="920">
@@ -38161,7 +38161,7 @@
         <v>15</v>
       </c>
       <c r="K920" t="n">
-        <v>5.257712056259166</v>
+        <v>5.250630632893348</v>
       </c>
     </row>
     <row r="921">
@@ -38202,7 +38202,7 @@
         <v>15</v>
       </c>
       <c r="K921" t="n">
-        <v>5.293517478008249</v>
+        <v>5.296436991846321</v>
       </c>
     </row>
     <row r="922">
@@ -38243,7 +38243,7 @@
         <v>15</v>
       </c>
       <c r="K922" t="n">
-        <v>5.293517478008249</v>
+        <v>5.296436991846321</v>
       </c>
     </row>
     <row r="923">
@@ -38284,7 +38284,7 @@
         <v>15</v>
       </c>
       <c r="K923" t="n">
-        <v>5.309289743892377</v>
+        <v>5.311194249405926</v>
       </c>
     </row>
     <row r="924">
@@ -38325,7 +38325,7 @@
         <v>15</v>
       </c>
       <c r="K924" t="n">
-        <v>5.309289743892377</v>
+        <v>5.311194249405926</v>
       </c>
     </row>
     <row r="925">
@@ -38366,7 +38366,7 @@
         <v>15</v>
       </c>
       <c r="K925" t="n">
-        <v>5.552818562652866</v>
+        <v>5.549644357065625</v>
       </c>
     </row>
     <row r="926">
@@ -38407,7 +38407,7 @@
         <v>15</v>
       </c>
       <c r="K926" t="n">
-        <v>5.937703266400429</v>
+        <v>5.938604201494719</v>
       </c>
     </row>
     <row r="927">
@@ -38448,7 +38448,7 @@
         <v>15</v>
       </c>
       <c r="K927" t="n">
-        <v>5.948223367941938</v>
+        <v>5.94587408235958</v>
       </c>
     </row>
     <row r="928">
@@ -38489,7 +38489,7 @@
         <v>15</v>
       </c>
       <c r="K928" t="n">
-        <v>5.981919514093581</v>
+        <v>5.983820383187557</v>
       </c>
     </row>
     <row r="929">
@@ -38530,7 +38530,7 @@
         <v>15</v>
       </c>
       <c r="K929" t="n">
-        <v>6.001880521486656</v>
+        <v>6.008621335011832</v>
       </c>
     </row>
     <row r="930">
@@ -38571,7 +38571,7 @@
         <v>15</v>
       </c>
       <c r="K930" t="n">
-        <v>6.025384264098518</v>
+        <v>6.025306545906821</v>
       </c>
     </row>
     <row r="931">
@@ -38612,7 +38612,7 @@
         <v>15</v>
       </c>
       <c r="K931" t="n">
-        <v>6.008189492129158</v>
+        <v>5.998660361227723</v>
       </c>
     </row>
     <row r="932">
@@ -38653,7 +38653,7 @@
         <v>15</v>
       </c>
       <c r="K932" t="n">
-        <v>6.008189492129158</v>
+        <v>5.998660361227723</v>
       </c>
     </row>
     <row r="933">
@@ -38694,7 +38694,7 @@
         <v>15</v>
       </c>
       <c r="K933" t="n">
-        <v>5.903918518139103</v>
+        <v>5.890796975409926</v>
       </c>
     </row>
     <row r="934">
@@ -38735,7 +38735,7 @@
         <v>15</v>
       </c>
       <c r="K934" t="n">
-        <v>5.903918518139103</v>
+        <v>5.890796975409926</v>
       </c>
     </row>
     <row r="935">
@@ -38776,7 +38776,7 @@
         <v>15</v>
       </c>
       <c r="K935" t="n">
-        <v>5.80211920165553</v>
+        <v>5.795673555103633</v>
       </c>
     </row>
     <row r="936">
@@ -38817,7 +38817,7 @@
         <v>15</v>
       </c>
       <c r="K936" t="n">
-        <v>5.729459463929304</v>
+        <v>5.721684878755669</v>
       </c>
     </row>
     <row r="937">
@@ -38858,7 +38858,7 @@
         <v>15</v>
       </c>
       <c r="K937" t="n">
-        <v>5.729459463929304</v>
+        <v>5.721684878755669</v>
       </c>
     </row>
     <row r="938">
@@ -38899,7 +38899,7 @@
         <v>15</v>
       </c>
       <c r="K938" t="n">
-        <v>5.499258924998848</v>
+        <v>5.498793201209439</v>
       </c>
     </row>
     <row r="939">
@@ -38940,7 +38940,7 @@
         <v>15</v>
       </c>
       <c r="K939" t="n">
-        <v>5.534225354218311</v>
+        <v>5.529595955230158</v>
       </c>
     </row>
     <row r="940">
@@ -38981,7 +38981,7 @@
         <v>15</v>
       </c>
       <c r="K940" t="n">
-        <v>5.639853908143159</v>
+        <v>5.638167967070005</v>
       </c>
     </row>
     <row r="941">
@@ -39022,7 +39022,7 @@
         <v>15</v>
       </c>
       <c r="K941" t="n">
-        <v>5.817572006514021</v>
+        <v>5.81675620168935</v>
       </c>
     </row>
     <row r="942">
@@ -39063,7 +39063,7 @@
         <v>15</v>
       </c>
       <c r="K942" t="n">
-        <v>6.09919952585834</v>
+        <v>6.099516592113219</v>
       </c>
     </row>
     <row r="943">
@@ -39104,7 +39104,7 @@
         <v>15</v>
       </c>
       <c r="K943" t="n">
-        <v>6.09919952585834</v>
+        <v>6.099516592113219</v>
       </c>
     </row>
     <row r="944">
@@ -39145,7 +39145,7 @@
         <v>15</v>
       </c>
       <c r="K944" t="n">
-        <v>6.432611099043855</v>
+        <v>6.432631010066814</v>
       </c>
     </row>
     <row r="945">
@@ -39186,7 +39186,7 @@
         <v>15</v>
       </c>
       <c r="K945" t="n">
-        <v>6.454452666983544</v>
+        <v>6.454472746028149</v>
       </c>
     </row>
     <row r="946">
@@ -39227,7 +39227,7 @@
         <v>15</v>
       </c>
       <c r="K946" t="n">
-        <v>6.442017129062031</v>
+        <v>6.443052489027956</v>
       </c>
     </row>
     <row r="947">
@@ -39268,7 +39268,7 @@
         <v>15</v>
       </c>
       <c r="K947" t="n">
-        <v>6.262730096678047</v>
+        <v>6.262561822518957</v>
       </c>
     </row>
     <row r="948">
@@ -39309,7 +39309,7 @@
         <v>15</v>
       </c>
       <c r="K948" t="n">
-        <v>5.924841031943818</v>
+        <v>5.924744826421659</v>
       </c>
     </row>
     <row r="949">
@@ -39350,7 +39350,7 @@
         <v>15</v>
       </c>
       <c r="K949" t="n">
-        <v>5.849009231374215</v>
+        <v>5.848905172473454</v>
       </c>
     </row>
     <row r="950">
@@ -39391,7 +39391,7 @@
         <v>15</v>
       </c>
       <c r="K950" t="n">
-        <v>5.705934934588075</v>
+        <v>5.705887851158268</v>
       </c>
     </row>
     <row r="951">
@@ -39432,7 +39432,7 @@
         <v>15</v>
       </c>
       <c r="K951" t="n">
-        <v>5.696561698421873</v>
+        <v>5.699535620530876</v>
       </c>
     </row>
     <row r="952">
@@ -39473,7 +39473,7 @@
         <v>15</v>
       </c>
       <c r="K952" t="n">
-        <v>5.578478408752981</v>
+        <v>5.578458948021187</v>
       </c>
     </row>
     <row r="953">
@@ -39514,7 +39514,7 @@
         <v>15</v>
       </c>
       <c r="K953" t="n">
-        <v>5.571208300624798</v>
+        <v>5.541805251625684</v>
       </c>
     </row>
     <row r="954">
@@ -39555,7 +39555,7 @@
         <v>15</v>
       </c>
       <c r="K954" t="n">
-        <v>5.537723179331093</v>
+        <v>5.539006485726673</v>
       </c>
     </row>
     <row r="955">
@@ -39596,7 +39596,7 @@
         <v>15</v>
       </c>
       <c r="K955" t="n">
-        <v>5.52228965360482</v>
+        <v>5.522257365072713</v>
       </c>
     </row>
     <row r="956">
@@ -39637,7 +39637,7 @@
         <v>15</v>
       </c>
       <c r="K956" t="n">
-        <v>5.540375638865029</v>
+        <v>5.540432915891826</v>
       </c>
     </row>
     <row r="957">
@@ -39678,7 +39678,7 @@
         <v>15</v>
       </c>
       <c r="K957" t="n">
-        <v>5.545879698110536</v>
+        <v>5.544083072530883</v>
       </c>
     </row>
     <row r="958">
@@ -39719,7 +39719,7 @@
         <v>15</v>
       </c>
       <c r="K958" t="n">
-        <v>5.628916862919725</v>
+        <v>5.626020054329989</v>
       </c>
     </row>
     <row r="959">
@@ -39760,7 +39760,7 @@
         <v>15</v>
       </c>
       <c r="K959" t="n">
-        <v>5.674917625192622</v>
+        <v>5.674967144936206</v>
       </c>
     </row>
     <row r="960">
@@ -39801,7 +39801,7 @@
         <v>15</v>
       </c>
       <c r="K960" t="n">
-        <v>5.929006448210383</v>
+        <v>5.925600518547506</v>
       </c>
     </row>
     <row r="961">
@@ -39842,7 +39842,7 @@
         <v>15</v>
       </c>
       <c r="K961" t="n">
-        <v>5.991074717736675</v>
+        <v>5.987195875122083</v>
       </c>
     </row>
     <row r="962">
@@ -39883,7 +39883,7 @@
         <v>15</v>
       </c>
       <c r="K962" t="n">
-        <v>6.298159195844231</v>
+        <v>6.298091342636818</v>
       </c>
     </row>
     <row r="963">
@@ -39924,7 +39924,7 @@
         <v>15</v>
       </c>
       <c r="K963" t="n">
-        <v>6.309837843789062</v>
+        <v>6.305956305056482</v>
       </c>
     </row>
     <row r="964">
@@ -39965,7 +39965,7 @@
         <v>15</v>
       </c>
       <c r="K964" t="n">
-        <v>6.44830340343425</v>
+        <v>6.444128328593207</v>
       </c>
     </row>
     <row r="965">
@@ -40006,7 +40006,7 @@
         <v>15</v>
       </c>
       <c r="K965" t="n">
-        <v>6.514856598967733</v>
+        <v>6.57237072530673</v>
       </c>
     </row>
     <row r="966">
@@ -40047,7 +40047,7 @@
         <v>15</v>
       </c>
       <c r="K966" t="n">
-        <v>6.735501466883139</v>
+        <v>6.730765308613821</v>
       </c>
     </row>
     <row r="967">
@@ -40088,7 +40088,7 @@
         <v>15</v>
       </c>
       <c r="K967" t="n">
-        <v>6.801499842439148</v>
+        <v>6.801399448402595</v>
       </c>
     </row>
     <row r="968">
@@ -40129,7 +40129,7 @@
         <v>15</v>
       </c>
       <c r="K968" t="n">
-        <v>6.863822239666854</v>
+        <v>6.863720682546699</v>
       </c>
     </row>
     <row r="969">
@@ -40170,7 +40170,7 @@
         <v>15</v>
       </c>
       <c r="K969" t="n">
-        <v>6.920113447049296</v>
+        <v>6.920113123854739</v>
       </c>
     </row>
     <row r="970">
@@ -40211,7 +40211,7 @@
         <v>15</v>
       </c>
       <c r="K970" t="n">
-        <v>6.918873414267013</v>
+        <v>6.919336069452331</v>
       </c>
     </row>
     <row r="971">
@@ -40252,7 +40252,7 @@
         <v>15</v>
       </c>
       <c r="K971" t="n">
-        <v>6.85260680063372</v>
+        <v>6.852688977050217</v>
       </c>
     </row>
     <row r="972">
@@ -40293,7 +40293,7 @@
         <v>15</v>
       </c>
       <c r="K972" t="n">
-        <v>6.802841101107148</v>
+        <v>6.80555333650629</v>
       </c>
     </row>
     <row r="973">
@@ -40334,7 +40334,7 @@
         <v>15</v>
       </c>
       <c r="K973" t="n">
-        <v>6.767023818287891</v>
+        <v>6.767149244076462</v>
       </c>
     </row>
     <row r="974">
@@ -40375,7 +40375,7 @@
         <v>15</v>
       </c>
       <c r="K974" t="n">
-        <v>6.614380026870976</v>
+        <v>6.614689532707477</v>
       </c>
     </row>
     <row r="975">
@@ -40416,7 +40416,7 @@
         <v>15</v>
       </c>
       <c r="K975" t="n">
-        <v>6.354903076137841</v>
+        <v>6.354898897358725</v>
       </c>
     </row>
     <row r="976">
@@ -40457,7 +40457,7 @@
         <v>15</v>
       </c>
       <c r="K976" t="n">
-        <v>6.314504165741719</v>
+        <v>6.314460673405075</v>
       </c>
     </row>
     <row r="977">
@@ -40498,7 +40498,7 @@
         <v>15</v>
       </c>
       <c r="K977" t="n">
-        <v>6.314504165741719</v>
+        <v>6.314460673405075</v>
       </c>
     </row>
     <row r="978">
@@ -40539,7 +40539,7 @@
         <v>15</v>
       </c>
       <c r="K978" t="n">
-        <v>6.256563321499864</v>
+        <v>6.25588923238192</v>
       </c>
     </row>
     <row r="979">
@@ -40580,7 +40580,7 @@
         <v>15</v>
       </c>
       <c r="K979" t="n">
-        <v>6.251672807717341</v>
+        <v>6.252860662191211</v>
       </c>
     </row>
     <row r="980">
@@ -40621,7 +40621,7 @@
         <v>15</v>
       </c>
       <c r="K980" t="n">
-        <v>6.230232563752237</v>
+        <v>6.231749488089136</v>
       </c>
     </row>
     <row r="981">
@@ -40662,7 +40662,7 @@
         <v>15</v>
       </c>
       <c r="K981" t="n">
-        <v>6.191679137226449</v>
+        <v>6.192896792814561</v>
       </c>
     </row>
     <row r="982">
@@ -40703,7 +40703,7 @@
         <v>15</v>
       </c>
       <c r="K982" t="n">
-        <v>6.191679137226449</v>
+        <v>6.192896792814561</v>
       </c>
     </row>
     <row r="983">
@@ -40744,7 +40744,7 @@
         <v>15</v>
       </c>
       <c r="K983" t="n">
-        <v>6.168171125531869</v>
+        <v>6.170187793622357</v>
       </c>
     </row>
     <row r="984">
@@ -40785,7 +40785,7 @@
         <v>15</v>
       </c>
       <c r="K984" t="n">
-        <v>6.162649015078597</v>
+        <v>6.170187793622357</v>
       </c>
     </row>
     <row r="985">
@@ -40826,7 +40826,7 @@
         <v>15</v>
       </c>
       <c r="K985" t="n">
-        <v>6.103943154388033</v>
+        <v>6.105398242323793</v>
       </c>
     </row>
     <row r="986">
@@ -40867,7 +40867,7 @@
         <v>15</v>
       </c>
       <c r="K986" t="n">
-        <v>6.117857131299487</v>
+        <v>6.117922228873477</v>
       </c>
     </row>
     <row r="987">
@@ -40908,7 +40908,7 @@
         <v>15</v>
       </c>
       <c r="K987" t="n">
-        <v>6.162024030535632</v>
+        <v>6.159949675333646</v>
       </c>
     </row>
     <row r="988">
@@ -40949,7 +40949,7 @@
         <v>15</v>
       </c>
       <c r="K988" t="n">
-        <v>6.138639977832082</v>
+        <v>6.139145373403164</v>
       </c>
     </row>
     <row r="989">
@@ -40990,7 +40990,7 @@
         <v>15</v>
       </c>
       <c r="K989" t="n">
-        <v>6.138639977832082</v>
+        <v>6.139145373403164</v>
       </c>
     </row>
     <row r="990">
@@ -41031,7 +41031,7 @@
         <v>15</v>
       </c>
       <c r="K990" t="n">
-        <v>6.071792911159609</v>
+        <v>6.078497194161093</v>
       </c>
     </row>
     <row r="991">
@@ -41072,7 +41072,7 @@
         <v>15</v>
       </c>
       <c r="K991" t="n">
-        <v>6.016907543842184</v>
+        <v>6.018511483185224</v>
       </c>
     </row>
     <row r="992">
@@ -41113,7 +41113,7 @@
         <v>15</v>
       </c>
       <c r="K992" t="n">
-        <v>6.016907543842184</v>
+        <v>6.018511483185224</v>
       </c>
     </row>
     <row r="993">
@@ -41154,7 +41154,7 @@
         <v>15</v>
       </c>
       <c r="K993" t="n">
-        <v>5.953933142918077</v>
+        <v>5.896572101796099</v>
       </c>
     </row>
     <row r="994">
@@ -41195,7 +41195,7 @@
         <v>15</v>
       </c>
       <c r="K994" t="n">
-        <v>5.812498906449565</v>
+        <v>5.812371496195909</v>
       </c>
     </row>
     <row r="995">
@@ -41236,7 +41236,7 @@
         <v>15</v>
       </c>
       <c r="K995" t="n">
-        <v>5.794096588962079</v>
+        <v>5.801920061879723</v>
       </c>
     </row>
     <row r="996">
@@ -41277,7 +41277,7 @@
         <v>15</v>
       </c>
       <c r="K996" t="n">
-        <v>5.614035638758709</v>
+        <v>5.619649959346084</v>
       </c>
     </row>
     <row r="997">
@@ -41318,7 +41318,7 @@
         <v>15</v>
       </c>
       <c r="K997" t="n">
-        <v>5.555064740291724</v>
+        <v>5.555175395136864</v>
       </c>
     </row>
     <row r="998">
@@ -41359,7 +41359,7 @@
         <v>15</v>
       </c>
       <c r="K998" t="n">
-        <v>5.506001569350206</v>
+        <v>5.506469392297957</v>
       </c>
     </row>
     <row r="999">
@@ -41400,7 +41400,7 @@
         <v>15</v>
       </c>
       <c r="K999" t="n">
-        <v>5.589193756830458</v>
+        <v>5.589222315552413</v>
       </c>
     </row>
     <row r="1000">
@@ -41441,7 +41441,7 @@
         <v>15</v>
       </c>
       <c r="K1000" t="n">
-        <v>5.660695299306921</v>
+        <v>5.66045014347386</v>
       </c>
     </row>
     <row r="1001">
@@ -41482,7 +41482,7 @@
         <v>15</v>
       </c>
       <c r="K1001" t="n">
-        <v>5.784517708734692</v>
+        <v>5.784392859259444</v>
       </c>
     </row>
     <row r="1002">
@@ -41523,7 +41523,7 @@
         <v>15</v>
       </c>
       <c r="K1002" t="n">
-        <v>5.784517708734692</v>
+        <v>5.784392859259444</v>
       </c>
     </row>
     <row r="1003">
@@ -41564,7 +41564,7 @@
         <v>15</v>
       </c>
       <c r="K1003" t="n">
-        <v>6.129378585154427</v>
+        <v>6.129219898365157</v>
       </c>
     </row>
     <row r="1004">
@@ -41605,7 +41605,7 @@
         <v>15</v>
       </c>
       <c r="K1004" t="n">
-        <v>6.663766660615069</v>
+        <v>6.663219432450753</v>
       </c>
     </row>
     <row r="1005">
@@ -41646,7 +41646,7 @@
         <v>15</v>
       </c>
       <c r="K1005" t="n">
-        <v>7.364673416106451</v>
+        <v>7.364120101405708</v>
       </c>
     </row>
     <row r="1006">
@@ -41687,7 +41687,7 @@
         <v>15</v>
       </c>
       <c r="K1006" t="n">
-        <v>8.005931502594262</v>
+        <v>8.006164474156169</v>
       </c>
     </row>
     <row r="1007">
@@ -41728,7 +41728,7 @@
         <v>15</v>
       </c>
       <c r="K1007" t="n">
-        <v>8.698563359166984</v>
+        <v>8.700337301594624</v>
       </c>
     </row>
     <row r="1008">
@@ -41769,7 +41769,7 @@
         <v>15</v>
       </c>
       <c r="K1008" t="n">
-        <v>9.126871719488522</v>
+        <v>9.130417031352442</v>
       </c>
     </row>
     <row r="1009">
@@ -41810,7 +41810,7 @@
         <v>15</v>
       </c>
       <c r="K1009" t="n">
-        <v>10.33169403302972</v>
+        <v>10.32241574369003</v>
       </c>
     </row>
     <row r="1010">
@@ -41851,7 +41851,7 @@
         <v>15</v>
       </c>
       <c r="K1010" t="n">
-        <v>10.93007656912688</v>
+        <v>10.80198683477333</v>
       </c>
     </row>
     <row r="1011">
@@ -41892,7 +41892,7 @@
         <v>15</v>
       </c>
       <c r="K1011" t="n">
-        <v>10.93007656912688</v>
+        <v>10.80198683477333</v>
       </c>
     </row>
     <row r="1012">
@@ -41933,7 +41933,7 @@
         <v>15</v>
       </c>
       <c r="K1012" t="n">
-        <v>10.94309617042991</v>
+        <v>10.81840893083375</v>
       </c>
     </row>
     <row r="1013">
@@ -41974,7 +41974,7 @@
         <v>15</v>
       </c>
       <c r="K1013" t="n">
-        <v>10.94309617042991</v>
+        <v>10.81840893083375</v>
       </c>
     </row>
     <row r="1014">
@@ -42015,7 +42015,7 @@
         <v>15</v>
       </c>
       <c r="K1014" t="n">
-        <v>10.13990999641341</v>
+        <v>10.18091717978264</v>
       </c>
     </row>
     <row r="1015">
@@ -42056,7 +42056,7 @@
         <v>15</v>
       </c>
       <c r="K1015" t="n">
-        <v>10.13990999641341</v>
+        <v>10.18091717978264</v>
       </c>
     </row>
     <row r="1016">
@@ -42097,7 +42097,7 @@
         <v>15</v>
       </c>
       <c r="K1016" t="n">
-        <v>9.085078495378276</v>
+        <v>9.110512055711229</v>
       </c>
     </row>
     <row r="1017">
@@ -42138,7 +42138,7 @@
         <v>15</v>
       </c>
       <c r="K1017" t="n">
-        <v>8.660066410722051</v>
+        <v>8.665281158715739</v>
       </c>
     </row>
     <row r="1018">
@@ -42179,7 +42179,7 @@
         <v>15</v>
       </c>
       <c r="K1018" t="n">
-        <v>8.660066410722051</v>
+        <v>8.665281158715739</v>
       </c>
     </row>
     <row r="1019">
@@ -42220,7 +42220,7 @@
         <v>15</v>
       </c>
       <c r="K1019" t="n">
-        <v>8.184083523870026</v>
+        <v>8.18366165578329</v>
       </c>
     </row>
     <row r="1020">
@@ -42261,7 +42261,7 @@
         <v>15</v>
       </c>
       <c r="K1020" t="n">
-        <v>7.710833425809165</v>
+        <v>7.709861632058381</v>
       </c>
     </row>
     <row r="1021">
@@ -42302,7 +42302,7 @@
         <v>15</v>
       </c>
       <c r="K1021" t="n">
-        <v>1.171105598571744</v>
+        <v>1.169501087172867</v>
       </c>
     </row>
     <row r="1022">
@@ -42343,7 +42343,7 @@
         <v>15</v>
       </c>
       <c r="K1022" t="n">
-        <v>1.171105598571744</v>
+        <v>1.169501087172867</v>
       </c>
     </row>
     <row r="1023">
@@ -42384,7 +42384,7 @@
         <v>15</v>
       </c>
       <c r="K1023" t="n">
-        <v>0.6678437509252654</v>
+        <v>0.6678245250579377</v>
       </c>
     </row>
     <row r="1024">
@@ -42425,7 +42425,7 @@
         <v>15</v>
       </c>
       <c r="K1024" t="n">
-        <v>0.6678437509252654</v>
+        <v>0.6678245250579377</v>
       </c>
     </row>
     <row r="1025">
@@ -42466,7 +42466,7 @@
         <v>15</v>
       </c>
       <c r="K1025" t="n">
-        <v>0.6475961261015692</v>
+        <v>0.6476102596682445</v>
       </c>
     </row>
     <row r="1026">
@@ -42507,7 +42507,7 @@
         <v>15</v>
       </c>
       <c r="K1026" t="n">
-        <v>0.6678207971184891</v>
+        <v>0.6678420448451642</v>
       </c>
     </row>
     <row r="1027">
@@ -42548,7 +42548,7 @@
         <v>15</v>
       </c>
       <c r="K1027" t="n">
-        <v>0.7174694513114023</v>
+        <v>0.7174812953194948</v>
       </c>
     </row>
     <row r="1028">
@@ -42589,7 +42589,7 @@
         <v>15</v>
       </c>
       <c r="K1028" t="n">
-        <v>0.7212327708383035</v>
+        <v>0.7212144891323027</v>
       </c>
     </row>
     <row r="1029">
@@ -42630,7 +42630,7 @@
         <v>15</v>
       </c>
       <c r="K1029" t="n">
-        <v>0.7212327708383035</v>
+        <v>0.7212144891323027</v>
       </c>
     </row>
     <row r="1030">
@@ -42671,7 +42671,7 @@
         <v>15</v>
       </c>
       <c r="K1030" t="n">
-        <v>0.5612866773092714</v>
+        <v>0.561270636065026</v>
       </c>
     </row>
     <row r="1031">
@@ -42712,7 +42712,7 @@
         <v>15</v>
       </c>
       <c r="K1031" t="n">
-        <v>0.5612866773092714</v>
+        <v>0.561270636065026</v>
       </c>
     </row>
     <row r="1032">
@@ -42753,7 +42753,7 @@
         <v>15</v>
       </c>
       <c r="K1032" t="n">
-        <v>0.4199952855991488</v>
+        <v>0.4199836428395714</v>
       </c>
     </row>
   </sheetData>
